--- a/Übungssammlung GGIE.xlsx
+++ b/Übungssammlung GGIE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carsteba\Nextcloud\Austausch_SOKO-L_Weiterentwicklung\Überarbeitung_Foliensätze\Block 7_SuS-Zusatzmodul\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carsteba\Nextcloud\Austausch_SOKO-L_Weiterentwicklung\Überarbeitung_Foliensätze\Block 7_SuS-Zusatzmodul\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F488F2-E8DC-4F08-81B4-EFBA0ABBD7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6881D5F9-F8AE-4B92-9511-80DB741FF649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-76920" yWindow="-14415" windowWidth="77040" windowHeight="31920" activeTab="1" xr2:uid="{5F5F4A6B-6BC2-42AB-AA6B-D27BC4305A0A}"/>
+    <workbookView xWindow="-73785" yWindow="-6720" windowWidth="57600" windowHeight="23445" activeTab="1" xr2:uid="{5F5F4A6B-6BC2-42AB-AA6B-D27BC4305A0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="529">
   <si>
     <t>PAGE URL</t>
   </si>
@@ -271,9 +271,6 @@
     <t>Hochschule</t>
   </si>
   <si>
-    <t>Altersstufe</t>
-  </si>
-  <si>
     <t>Dauer</t>
   </si>
   <si>
@@ -458,9 +455,6 @@
   </si>
   <si>
     <t>Social Awareness</t>
-  </si>
-  <si>
-    <t>Mindfulness Components</t>
   </si>
   <si>
     <t>Open Awareness</t>
@@ -502,9 +496,6 @@
     <t>Fairness
 Teamwork
 Collaboration</t>
-  </si>
-  <si>
-    <t>SEL-COMPONENTS</t>
   </si>
   <si>
     <t>Non-Judgment</t>
@@ -1027,9 +1018,6 @@
   </si>
   <si>
     <t>Resp. Decision-Making</t>
-  </si>
-  <si>
-    <t>Durchführung</t>
   </si>
   <si>
     <t>Vorher</t>
@@ -3442,7 +3430,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3457,18 +3445,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -3990,7 +3966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B052A52-8AEB-4197-AC75-1AB8165A213A}">
-  <dimension ref="A1:AB70"/>
+  <dimension ref="A1:AB69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="255.5703125" customWidth="1"/>
@@ -4024,192 +4000,239 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="G1" s="12" t="s">
+      <c r="A1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="Q1" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
+      <c r="F1" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>237</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    <row r="2" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="T2" s="6" t="s">
+      <c r="F2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="U2" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="W2" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="X2" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>241</v>
+      <c r="P2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="N3" t="s">
-        <v>147</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="P3" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>1</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>1</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="375" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>108</v>
@@ -4221,13 +4244,13 @@
         <v>79</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -4236,54 +4259,54 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q4">
+        <v>158</v>
+      </c>
+      <c r="Q4" s="1">
         <v>1</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>1</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
         <v>1</v>
       </c>
       <c r="AB4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="375" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
         <v>109</v>
@@ -4292,13 +4315,13 @@
         <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -4316,18 +4339,18 @@
         <v>0</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N5" t="s">
+        <v>160</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q5" s="1">
+      <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
@@ -4336,28 +4359,28 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0</v>
-      </c>
-      <c r="V5" s="1">
-        <v>1</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0</v>
-      </c>
-      <c r="X5" s="1">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
         <v>1</v>
       </c>
       <c r="AB5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
         <v>110</v>
@@ -4366,13 +4389,13 @@
         <v>87</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -4384,22 +4407,22 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="N6" t="s">
-        <v>163</v>
+        <v>140</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4408,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4420,18 +4443,18 @@
         <v>1</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
         <v>111</v>
@@ -4443,7 +4466,7 @@
         <v>79</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4464,16 +4487,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -4488,24 +4511,24 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <v>1</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
         <v>112</v>
@@ -4517,13 +4540,13 @@
         <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4538,16 +4561,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -4556,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8">
         <v>1</v>
@@ -4574,12 +4597,12 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>113</v>
@@ -4588,16 +4611,16 @@
         <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -4612,10 +4635,10 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>171</v>
@@ -4633,10 +4656,10 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>1</v>
@@ -4648,27 +4671,27 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -4689,28 +4712,28 @@
         <v>173</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
         <v>1</v>
@@ -4719,18 +4742,18 @@
         <v>1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>92</v>
@@ -4739,7 +4762,7 @@
         <v>79</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -4760,16 +4783,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -4796,12 +4819,12 @@
         <v>1</v>
       </c>
       <c r="AB11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="135" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
         <v>115</v>
@@ -4810,10 +4833,10 @@
         <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -4834,22 +4857,22 @@
         <v>0</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -4870,12 +4893,12 @@
         <v>1</v>
       </c>
       <c r="AB12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
         <v>116</v>
@@ -4884,13 +4907,13 @@
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -4905,37 +4928,37 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13">
         <v>1</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13">
         <v>1</v>
@@ -4944,12 +4967,12 @@
         <v>1</v>
       </c>
       <c r="AB13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
         <v>117</v>
@@ -4961,13 +4984,13 @@
         <v>81</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -4979,19 +5002,19 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -5003,13 +5026,13 @@
         <v>1</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14">
         <v>1</v>
@@ -5018,12 +5041,12 @@
         <v>1</v>
       </c>
       <c r="AB14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
         <v>118</v>
@@ -5032,10 +5055,10 @@
         <v>96</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -5056,16 +5079,16 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -5080,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>1</v>
@@ -5092,12 +5115,12 @@
         <v>1</v>
       </c>
       <c r="AB15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>119</v>
@@ -5106,10 +5129,10 @@
         <v>97</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -5118,25 +5141,25 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>199</v>
@@ -5154,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16">
         <v>1</v>
@@ -5166,12 +5189,12 @@
         <v>1</v>
       </c>
       <c r="AB16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="195" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
         <v>120</v>
@@ -5183,46 +5206,46 @@
         <v>79</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <v>1</v>
@@ -5234,33 +5257,33 @@
         <v>1</v>
       </c>
       <c r="W17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="AB17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -5278,48 +5301,48 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
         <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18">
         <v>1</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="AB18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
         <v>128</v>
@@ -5328,46 +5351,46 @@
         <v>100</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
         <v>1</v>
@@ -5376,45 +5399,45 @@
         <v>1</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
       <c r="AB19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>261</v>
+      <c r="E20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -5423,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>215</v>
@@ -5441,75 +5464,84 @@
         <v>1</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>1</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
+      <c r="Y20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>255</v>
+      </c>
       <c r="AB20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>217</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -5530,27 +5562,27 @@
         <v>0</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21">
         <v>1</v>
       </c>
-      <c r="Y21" t="s">
-        <v>257</v>
+      <c r="Y21" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>259</v>
+        <v>251</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="AB21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="315" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
         <v>122</v>
@@ -5559,10 +5591,10 @@
         <v>103</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5571,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -5580,13 +5612,13 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>222</v>
@@ -5601,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -5610,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -5618,22 +5650,22 @@
       <c r="X22">
         <v>1</v>
       </c>
-      <c r="Y22" s="1" t="s">
-        <v>254</v>
+      <c r="Y22" t="s">
+        <v>247</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>249</v>
       </c>
       <c r="AB22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="315" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
         <v>123</v>
@@ -5642,16 +5674,16 @@
         <v>104</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -5663,13 +5695,13 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>224</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>225</v>
@@ -5681,7 +5713,7 @@
         <v>1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5690,33 +5722,33 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23">
         <v>1</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AA23" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AB23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
         <v>124</v>
@@ -5725,16 +5757,16 @@
         <v>105</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -5746,19 +5778,19 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>227</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -5767,42 +5799,42 @@
         <v>1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>1</v>
       </c>
       <c r="W24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AA24" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AB24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>106</v>
@@ -5811,7 +5843,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5832,10 +5864,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>231</v>
+        <v>145</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>232</v>
@@ -5853,164 +5885,164 @@
         <v>1</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25">
         <v>0</v>
       </c>
       <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>245</v>
+        <v>1</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>247</v>
+        <v>239</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="AB25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>1</v>
-      </c>
-      <c r="T26">
-        <v>1</v>
-      </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA26" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>71</v>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="10">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="10">
+        <v>0</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>1</v>
+      </c>
+      <c r="R26" s="10">
+        <v>1</v>
+      </c>
+      <c r="S26" s="10">
+        <v>1</v>
+      </c>
+      <c r="T26" s="10">
+        <v>1</v>
+      </c>
+      <c r="U26" s="10">
+        <v>0</v>
+      </c>
+      <c r="V26" s="10">
+        <v>1</v>
+      </c>
+      <c r="W26" s="10">
+        <v>1</v>
+      </c>
+      <c r="X26" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="Z26" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="AA26" s="10" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="E27" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10">
+        <v>1</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
+        <v>0</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="O27" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" s="10">
-        <v>1</v>
-      </c>
-      <c r="H27" s="10">
-        <v>0</v>
-      </c>
-      <c r="I27" s="10">
-        <v>0</v>
-      </c>
-      <c r="J27" s="10">
-        <v>0</v>
-      </c>
-      <c r="K27" s="10">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10">
-        <v>0</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>274</v>
-      </c>
       <c r="P27" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="Q27" s="10">
         <v>1</v>
@@ -6025,42 +6057,42 @@
         <v>1</v>
       </c>
       <c r="U27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="10">
         <v>1</v>
       </c>
       <c r="W27" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" s="10">
         <v>1</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="AA27" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -6084,16 +6116,16 @@
         <v>0</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="O28" s="10" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Q28" s="10">
         <v>1</v>
@@ -6105,45 +6137,45 @@
         <v>1</v>
       </c>
       <c r="T28" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="10">
         <v>1</v>
       </c>
       <c r="W28" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="10">
         <v>1</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="AA28" s="10" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -6167,16 +6199,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>295</v>
+        <v>300</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>301</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q29" s="10">
         <v>1</v>
@@ -6185,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -6203,63 +6235,63 @@
         <v>1</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AA29" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10">
+        <v>0</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" s="10">
-        <v>1</v>
-      </c>
-      <c r="H30" s="10">
-        <v>0</v>
-      </c>
-      <c r="I30" s="10">
-        <v>0</v>
-      </c>
-      <c r="J30" s="10">
-        <v>0</v>
-      </c>
-      <c r="K30" s="10">
-        <v>0</v>
-      </c>
-      <c r="L30" s="10">
-        <v>0</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>305</v>
-      </c>
       <c r="O30" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="Q30" s="10">
         <v>1</v>
@@ -6268,10 +6300,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="10">
         <v>0</v>
@@ -6286,30 +6318,30 @@
         <v>1</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AA30" s="10" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -6333,16 +6365,16 @@
         <v>0</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="Q31" s="10">
         <v>1</v>
@@ -6357,123 +6389,121 @@
         <v>1</v>
       </c>
       <c r="U31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="10">
         <v>1</v>
       </c>
       <c r="W31" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" s="10">
         <v>1</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="Z31" s="10" t="s">
         <v>315</v>
       </c>
       <c r="AA31" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C32" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>1</v>
+      </c>
+      <c r="R32" s="10">
+        <v>1</v>
+      </c>
+      <c r="S32" s="10">
+        <v>1</v>
+      </c>
+      <c r="T32" s="10">
+        <v>0</v>
+      </c>
+      <c r="U32" s="10">
+        <v>0</v>
+      </c>
+      <c r="V32" s="10">
+        <v>1</v>
+      </c>
+      <c r="W32" s="10">
+        <v>1</v>
+      </c>
+      <c r="X32" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z32" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" s="10">
-        <v>1</v>
-      </c>
-      <c r="H32" s="10">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10">
-        <v>0</v>
-      </c>
-      <c r="J32" s="10">
-        <v>0</v>
-      </c>
-      <c r="K32" s="10">
-        <v>0</v>
-      </c>
-      <c r="L32" s="10">
-        <v>0</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="O32" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="P32" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q32" s="10">
-        <v>1</v>
-      </c>
-      <c r="R32" s="10">
-        <v>1</v>
-      </c>
-      <c r="S32" s="10">
-        <v>1</v>
-      </c>
-      <c r="T32" s="10">
-        <v>1</v>
-      </c>
-      <c r="U32" s="10">
-        <v>1</v>
-      </c>
-      <c r="V32" s="10">
-        <v>1</v>
-      </c>
-      <c r="W32" s="10">
-        <v>0</v>
-      </c>
-      <c r="X32" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="Z32" s="10" t="s">
-        <v>319</v>
-      </c>
       <c r="AA32" s="10" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -6497,64 +6527,66 @@
         <v>0</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>295</v>
+        <v>300</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>301</v>
       </c>
       <c r="O33" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>1</v>
+      </c>
+      <c r="R33" s="10">
+        <v>1</v>
+      </c>
+      <c r="S33" s="10">
+        <v>0</v>
+      </c>
+      <c r="T33" s="10">
+        <v>0</v>
+      </c>
+      <c r="U33" s="10">
+        <v>0</v>
+      </c>
+      <c r="V33" s="10">
+        <v>1</v>
+      </c>
+      <c r="W33" s="10">
+        <v>1</v>
+      </c>
+      <c r="X33" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="Z33" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="P33" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q33" s="10">
-        <v>1</v>
-      </c>
-      <c r="R33" s="10">
-        <v>1</v>
-      </c>
-      <c r="S33" s="10">
-        <v>1</v>
-      </c>
-      <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="10">
-        <v>0</v>
-      </c>
-      <c r="V33" s="10">
-        <v>1</v>
-      </c>
-      <c r="W33" s="10">
-        <v>1</v>
-      </c>
-      <c r="X33" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z33" s="10" t="s">
-        <v>324</v>
-      </c>
       <c r="AA33" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="D34" s="10"/>
+      <c r="D34" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="E34" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -6578,16 +6610,16 @@
         <v>0</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>305</v>
+        <v>326</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="O34" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="Q34" s="10">
         <v>1</v>
@@ -6596,10 +6628,10 @@
         <v>1</v>
       </c>
       <c r="S34" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="10">
         <v>0</v>
@@ -6614,30 +6646,30 @@
         <v>1</v>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="Z34" s="10" t="s">
         <v>327</v>
       </c>
       <c r="AA34" s="10" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>266</v>
+        <v>330</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -6661,16 +6693,16 @@
         <v>0</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="Q35" s="10">
         <v>1</v>
@@ -6685,25 +6717,25 @@
         <v>1</v>
       </c>
       <c r="U35" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="10">
         <v>1</v>
       </c>
       <c r="W35" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" s="10">
         <v>1</v>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="Z35" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA35" s="10" t="s">
-        <v>332</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -6717,10 +6749,10 @@
         <v>335</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -6744,16 +6776,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>285</v>
+        <v>290</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>355</v>
       </c>
       <c r="O36" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="Q36" s="10">
         <v>1</v>
@@ -6765,45 +6797,45 @@
         <v>1</v>
       </c>
       <c r="T36" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="10">
         <v>1</v>
       </c>
       <c r="W36" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" s="10">
         <v>1</v>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA36" s="10" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -6827,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="Q37" s="10">
         <v>1</v>
@@ -6845,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -6863,39 +6895,39 @@
         <v>1</v>
       </c>
       <c r="Y37" s="10" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA37" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="10">
         <v>0</v>
@@ -6910,16 +6942,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="N38" s="10" t="s">
-        <v>305</v>
+        <v>267</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="O38" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="Q38" s="10">
         <v>1</v>
@@ -6928,10 +6960,10 @@
         <v>1</v>
       </c>
       <c r="S38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="10">
         <v>0</v>
@@ -6946,13 +6978,13 @@
         <v>1</v>
       </c>
       <c r="Y38" s="10" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="Z38" s="10" t="s">
         <v>347</v>
       </c>
       <c r="AA38" s="10" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
@@ -6966,10 +6998,10 @@
         <v>350</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -6993,16 +7025,16 @@
         <v>0</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="Q39" s="10">
         <v>1</v>
@@ -7017,25 +7049,25 @@
         <v>1</v>
       </c>
       <c r="U39" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="10">
         <v>1</v>
       </c>
       <c r="W39" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" s="10">
         <v>1</v>
       </c>
       <c r="Y39" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="Z39" s="10" t="s">
         <v>351</v>
       </c>
       <c r="AA39" s="10" t="s">
-        <v>278</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
@@ -7049,10 +7081,10 @@
         <v>354</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -7076,16 +7108,16 @@
         <v>0</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>285</v>
+        <v>290</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>355</v>
       </c>
       <c r="O40" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Q40" s="10">
         <v>1</v>
@@ -7097,45 +7129,45 @@
         <v>1</v>
       </c>
       <c r="T40" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="10">
         <v>1</v>
       </c>
       <c r="W40" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" s="10">
         <v>1</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA40" s="10" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -7159,16 +7191,16 @@
         <v>0</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q41" s="10">
         <v>1</v>
@@ -7177,7 +7209,7 @@
         <v>1</v>
       </c>
       <c r="S41" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -7195,13 +7227,13 @@
         <v>1</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="Z41" s="10" t="s">
         <v>360</v>
       </c>
       <c r="AA41" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
@@ -7215,10 +7247,10 @@
         <v>363</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -7242,16 +7274,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>305</v>
+        <v>267</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="O42" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="Q42" s="10">
         <v>1</v>
@@ -7260,10 +7292,10 @@
         <v>1</v>
       </c>
       <c r="S42" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" s="10">
         <v>0</v>
@@ -7278,13 +7310,13 @@
         <v>1</v>
       </c>
       <c r="Y42" s="10" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="Z42" s="10" t="s">
         <v>364</v>
       </c>
       <c r="AA42" s="10" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
@@ -7298,10 +7330,10 @@
         <v>367</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -7325,16 +7357,16 @@
         <v>0</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="Q43" s="10">
         <v>1</v>
@@ -7349,25 +7381,25 @@
         <v>1</v>
       </c>
       <c r="U43" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="10">
         <v>1</v>
       </c>
       <c r="W43" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X43" s="10">
         <v>1</v>
       </c>
       <c r="Y43" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="Z43" s="10" t="s">
         <v>368</v>
       </c>
       <c r="AA43" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
@@ -7381,10 +7413,10 @@
         <v>371</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -7408,16 +7440,16 @@
         <v>0</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>285</v>
+        <v>290</v>
+      </c>
+      <c r="N44" s="10" t="s">
+        <v>355</v>
       </c>
       <c r="O44" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Q44" s="10">
         <v>1</v>
@@ -7429,28 +7461,28 @@
         <v>1</v>
       </c>
       <c r="T44" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="10">
         <v>1</v>
       </c>
       <c r="W44" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" s="10">
         <v>1</v>
       </c>
       <c r="Y44" s="10" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Z44" s="10" t="s">
         <v>372</v>
       </c>
       <c r="AA44" s="10" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
@@ -7464,43 +7496,43 @@
         <v>375</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
-      <c r="G45" s="10">
-        <v>0</v>
-      </c>
-      <c r="H45" s="10">
-        <v>1</v>
-      </c>
-      <c r="I45" s="10">
-        <v>0</v>
-      </c>
-      <c r="J45" s="10">
-        <v>0</v>
-      </c>
-      <c r="K45" s="10">
-        <v>0</v>
-      </c>
-      <c r="L45" s="10">
+      <c r="G45" s="11">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11">
+        <v>1</v>
+      </c>
+      <c r="I45" s="11">
+        <v>0</v>
+      </c>
+      <c r="J45" s="11">
+        <v>0</v>
+      </c>
+      <c r="K45" s="11">
+        <v>0</v>
+      </c>
+      <c r="L45" s="11">
         <v>0</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q45" s="10">
         <v>1</v>
@@ -7509,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="S45" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
@@ -7527,13 +7559,13 @@
         <v>1</v>
       </c>
       <c r="Y45" s="10" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="Z45" s="10" t="s">
         <v>376</v>
       </c>
       <c r="AA45" s="10" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
@@ -7547,10 +7579,10 @@
         <v>379</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -7559,10 +7591,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="11">
         <v>0</v>
@@ -7574,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>305</v>
+        <v>267</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="Q46" s="10">
         <v>1</v>
@@ -7592,10 +7624,10 @@
         <v>1</v>
       </c>
       <c r="S46" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" s="10">
         <v>0</v>
@@ -7610,13 +7642,13 @@
         <v>1</v>
       </c>
       <c r="Y46" s="10" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="Z46" s="10" t="s">
         <v>380</v>
       </c>
       <c r="AA46" s="10" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
@@ -7630,10 +7662,10 @@
         <v>383</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -7657,16 +7689,16 @@
         <v>0</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="Q47" s="10">
         <v>1</v>
@@ -7681,25 +7713,25 @@
         <v>1</v>
       </c>
       <c r="U47" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="10">
         <v>1</v>
       </c>
       <c r="W47" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X47" s="10">
         <v>1</v>
       </c>
       <c r="Y47" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="Z47" s="10" t="s">
         <v>384</v>
       </c>
       <c r="AA47" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
@@ -7713,10 +7745,10 @@
         <v>387</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -7740,16 +7772,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>285</v>
+        <v>300</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>301</v>
       </c>
       <c r="O48" s="10" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="Q48" s="10">
         <v>1</v>
@@ -7758,31 +7790,31 @@
         <v>1</v>
       </c>
       <c r="S48" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="10">
         <v>1</v>
       </c>
       <c r="W48" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10">
         <v>1</v>
       </c>
       <c r="Y48" s="10" t="s">
-        <v>288</v>
+        <v>342</v>
       </c>
       <c r="Z48" s="10" t="s">
         <v>388</v>
       </c>
       <c r="AA48" s="10" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
@@ -7793,46 +7825,46 @@
         <v>390</v>
       </c>
       <c r="C49" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" s="11">
+        <v>0</v>
+      </c>
+      <c r="H49" s="11">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11">
+        <v>1</v>
+      </c>
+      <c r="J49" s="11">
+        <v>0</v>
+      </c>
+      <c r="K49" s="11">
+        <v>0</v>
+      </c>
+      <c r="L49" s="11">
+        <v>0</v>
+      </c>
+      <c r="M49" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="D49" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" s="11">
-        <v>0</v>
-      </c>
-      <c r="H49" s="11">
-        <v>0</v>
-      </c>
-      <c r="I49" s="11">
-        <v>1</v>
-      </c>
-      <c r="J49" s="11">
-        <v>0</v>
-      </c>
-      <c r="K49" s="11">
-        <v>0</v>
-      </c>
-      <c r="L49" s="11">
-        <v>0</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>305</v>
+      <c r="N49" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="Q49" s="10">
         <v>1</v>
@@ -7841,10 +7873,10 @@
         <v>1</v>
       </c>
       <c r="S49" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" s="10">
         <v>0</v>
@@ -7859,30 +7891,30 @@
         <v>1</v>
       </c>
       <c r="Y49" s="10" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="Z49" s="10" t="s">
         <v>392</v>
       </c>
       <c r="AA49" s="10" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>394</v>
-      </c>
       <c r="C50" s="10" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -7906,182 +7938,182 @@
         <v>0</v>
       </c>
       <c r="M50" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="N50" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q50" s="10">
+        <v>1</v>
+      </c>
+      <c r="R50" s="10">
+        <v>1</v>
+      </c>
+      <c r="S50" s="10">
+        <v>1</v>
+      </c>
+      <c r="T50" s="10">
+        <v>1</v>
+      </c>
+      <c r="U50" s="10">
+        <v>1</v>
+      </c>
+      <c r="V50" s="10">
+        <v>1</v>
+      </c>
+      <c r="W50" s="10">
+        <v>0</v>
+      </c>
+      <c r="X50" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z50" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="N50" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="O50" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="P50" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q50" s="10">
-        <v>1</v>
-      </c>
-      <c r="R50" s="10">
-        <v>1</v>
-      </c>
-      <c r="S50" s="10">
-        <v>1</v>
-      </c>
-      <c r="T50" s="10">
-        <v>1</v>
-      </c>
-      <c r="U50" s="10">
-        <v>0</v>
-      </c>
-      <c r="V50" s="10">
-        <v>1</v>
-      </c>
-      <c r="W50" s="10">
-        <v>1</v>
-      </c>
-      <c r="X50" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z50" s="10" t="s">
-        <v>396</v>
-      </c>
       <c r="AA50" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>397</v>
       </c>
       <c r="C51" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" s="11">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11">
+        <v>1</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0</v>
+      </c>
+      <c r="K51" s="11">
+        <v>0</v>
+      </c>
+      <c r="L51" s="11">
+        <v>0</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q51" s="10">
+        <v>1</v>
+      </c>
+      <c r="R51" s="10">
+        <v>1</v>
+      </c>
+      <c r="S51" s="10">
+        <v>1</v>
+      </c>
+      <c r="T51" s="10">
+        <v>0</v>
+      </c>
+      <c r="U51" s="10">
+        <v>0</v>
+      </c>
+      <c r="V51" s="10">
+        <v>1</v>
+      </c>
+      <c r="W51" s="10">
+        <v>1</v>
+      </c>
+      <c r="X51" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z51" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA51" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" s="11">
-        <v>0</v>
-      </c>
-      <c r="H51" s="11">
-        <v>0</v>
-      </c>
-      <c r="I51" s="11">
-        <v>1</v>
-      </c>
-      <c r="J51" s="11">
-        <v>0</v>
-      </c>
-      <c r="K51" s="11">
-        <v>0</v>
-      </c>
-      <c r="L51" s="11">
-        <v>0</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q51" s="10">
-        <v>1</v>
-      </c>
-      <c r="R51" s="10">
-        <v>1</v>
-      </c>
-      <c r="S51" s="10">
-        <v>1</v>
-      </c>
-      <c r="T51" s="10">
-        <v>1</v>
-      </c>
-      <c r="U51" s="10">
-        <v>1</v>
-      </c>
-      <c r="V51" s="10">
-        <v>1</v>
-      </c>
-      <c r="W51" s="10">
-        <v>0</v>
-      </c>
-      <c r="X51" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y51" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="Z51" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="AA51" s="10" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" s="11">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11">
+        <v>1</v>
+      </c>
+      <c r="J52" s="11">
+        <v>0</v>
+      </c>
+      <c r="K52" s="11">
+        <v>0</v>
+      </c>
+      <c r="L52" s="11">
+        <v>0</v>
+      </c>
+      <c r="M52" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52" s="11">
-        <v>0</v>
-      </c>
-      <c r="H52" s="11">
-        <v>0</v>
-      </c>
-      <c r="I52" s="11">
-        <v>1</v>
-      </c>
-      <c r="J52" s="11">
-        <v>0</v>
-      </c>
-      <c r="K52" s="11">
-        <v>0</v>
-      </c>
-      <c r="L52" s="11">
-        <v>0</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>405</v>
-      </c>
       <c r="N52" s="10" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O52" s="10" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="P52" s="10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q52" s="10">
         <v>1</v>
@@ -8090,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="S52" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" s="10">
         <v>0</v>
@@ -8108,13 +8140,13 @@
         <v>1</v>
       </c>
       <c r="Y52" s="10" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="Z52" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA52" s="10" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.25">
@@ -8125,22 +8157,22 @@
         <v>409</v>
       </c>
       <c r="C53" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>303</v>
-      </c>
       <c r="E53" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="11">
         <v>1</v>
@@ -8155,16 +8187,16 @@
         <v>0</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>405</v>
+        <v>267</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>305</v>
+        <v>412</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>306</v>
+        <v>413</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>307</v>
+        <v>414</v>
       </c>
       <c r="Q53" s="10">
         <v>1</v>
@@ -8182,203 +8214,203 @@
         <v>0</v>
       </c>
       <c r="V53" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X53" s="10">
         <v>1</v>
       </c>
       <c r="Y53" s="10" t="s">
-        <v>346</v>
+        <v>415</v>
       </c>
       <c r="Z53" s="10" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AA53" s="10" t="s">
-        <v>310</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B54" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" s="11">
+        <v>1</v>
+      </c>
+      <c r="H54" s="11">
+        <v>1</v>
+      </c>
+      <c r="I54" s="11">
+        <v>1</v>
+      </c>
+      <c r="J54" s="11">
+        <v>0</v>
+      </c>
+      <c r="K54" s="11">
+        <v>0</v>
+      </c>
+      <c r="L54" s="11">
+        <v>0</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="O54" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="P54" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q54" s="10">
+        <v>1</v>
+      </c>
+      <c r="R54" s="10">
+        <v>1</v>
+      </c>
+      <c r="S54" s="10">
+        <v>0</v>
+      </c>
+      <c r="T54" s="10">
+        <v>0</v>
+      </c>
+      <c r="U54" s="10">
+        <v>0</v>
+      </c>
+      <c r="V54" s="10">
+        <v>0</v>
+      </c>
+      <c r="W54" s="10">
+        <v>0</v>
+      </c>
+      <c r="X54" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54">
-        <v>1</v>
-      </c>
-      <c r="G54" s="11">
-        <v>1</v>
-      </c>
-      <c r="H54" s="11">
-        <v>1</v>
-      </c>
-      <c r="I54" s="11">
-        <v>1</v>
-      </c>
-      <c r="J54" s="11">
-        <v>0</v>
-      </c>
-      <c r="K54" s="11">
-        <v>0</v>
-      </c>
-      <c r="L54" s="11">
-        <v>0</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="N54" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="O54" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="P54" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q54" s="10">
-        <v>1</v>
-      </c>
-      <c r="R54" s="10">
-        <v>1</v>
-      </c>
-      <c r="S54" s="10">
-        <v>0</v>
-      </c>
-      <c r="T54" s="10">
-        <v>0</v>
-      </c>
-      <c r="U54" s="10">
-        <v>0</v>
-      </c>
-      <c r="V54" s="10">
-        <v>0</v>
-      </c>
-      <c r="W54" s="10">
-        <v>0</v>
-      </c>
-      <c r="X54" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y54" s="10" t="s">
-        <v>419</v>
-      </c>
       <c r="Z54" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AA54" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" s="11">
+        <v>1</v>
+      </c>
+      <c r="H55" s="11">
+        <v>1</v>
+      </c>
+      <c r="I55" s="11">
+        <v>1</v>
+      </c>
+      <c r="J55" s="11">
+        <v>0</v>
+      </c>
+      <c r="K55" s="11">
+        <v>0</v>
+      </c>
+      <c r="L55" s="11">
+        <v>0</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="N55" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C55" s="10" t="s">
+      <c r="O55" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q55" s="10">
+        <v>1</v>
+      </c>
+      <c r="R55" s="10">
+        <v>1</v>
+      </c>
+      <c r="S55" s="10">
+        <v>0</v>
+      </c>
+      <c r="T55" s="10">
+        <v>0</v>
+      </c>
+      <c r="U55" s="10">
+        <v>0</v>
+      </c>
+      <c r="V55" s="10">
+        <v>0</v>
+      </c>
+      <c r="W55" s="10">
+        <v>0</v>
+      </c>
+      <c r="X55" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="Z55" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="AA55" s="10" t="s">
         <v>424</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" s="11">
-        <v>1</v>
-      </c>
-      <c r="H55" s="11">
-        <v>1</v>
-      </c>
-      <c r="I55" s="11">
-        <v>1</v>
-      </c>
-      <c r="J55" s="11">
-        <v>0</v>
-      </c>
-      <c r="K55" s="11">
-        <v>0</v>
-      </c>
-      <c r="L55" s="11">
-        <v>0</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q55" s="10">
-        <v>1</v>
-      </c>
-      <c r="R55" s="10">
-        <v>1</v>
-      </c>
-      <c r="S55" s="10">
-        <v>0</v>
-      </c>
-      <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="10">
-        <v>0</v>
-      </c>
-      <c r="V55" s="10">
-        <v>0</v>
-      </c>
-      <c r="W55" s="10">
-        <v>0</v>
-      </c>
-      <c r="X55" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y55" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="Z55" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="AA55" s="10" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
-        <v>431</v>
+      <c r="A56" s="9" t="s">
+        <v>430</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>429</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="D56" s="10"/>
+        <v>431</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>432</v>
+      </c>
       <c r="E56" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -8402,16 +8434,16 @@
         <v>0</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="O56" s="10" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Q56" s="10">
         <v>1</v>
@@ -8438,30 +8470,30 @@
         <v>1</v>
       </c>
       <c r="Y56" s="10" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="Z56" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AA56" s="10" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>436</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -8485,16 +8517,16 @@
         <v>0</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Q57" s="10">
         <v>1</v>
@@ -8521,30 +8553,30 @@
         <v>1</v>
       </c>
       <c r="Y57" s="10" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="Z57" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AA57" s="10" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -8568,25 +8600,23 @@
         <v>0</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="O58" s="10" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q58" s="10">
-        <v>1</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="Q58" s="10"/>
       <c r="R58" s="10">
         <v>1</v>
       </c>
       <c r="S58" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="10">
         <v>0</v>
@@ -8604,111 +8634,113 @@
         <v>1</v>
       </c>
       <c r="Y58" s="10" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="Z58" s="10" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AA58" s="10" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="11">
+        <v>1</v>
+      </c>
+      <c r="H59" s="11">
+        <v>1</v>
+      </c>
+      <c r="I59" s="11">
+        <v>1</v>
+      </c>
+      <c r="J59" s="11">
+        <v>0</v>
+      </c>
+      <c r="K59" s="11">
+        <v>0</v>
+      </c>
+      <c r="L59" s="11">
+        <v>0</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="C59" s="10" t="s">
+      <c r="Q59" s="10">
+        <v>1</v>
+      </c>
+      <c r="R59" s="10">
+        <v>1</v>
+      </c>
+      <c r="S59" s="10">
+        <v>0</v>
+      </c>
+      <c r="T59" s="10">
+        <v>0</v>
+      </c>
+      <c r="U59" s="10">
+        <v>0</v>
+      </c>
+      <c r="V59" s="10">
+        <v>0</v>
+      </c>
+      <c r="W59" s="10">
+        <v>0</v>
+      </c>
+      <c r="X59" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="D59" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" s="11">
-        <v>1</v>
-      </c>
-      <c r="H59" s="11">
-        <v>1</v>
-      </c>
-      <c r="I59" s="11">
-        <v>1</v>
-      </c>
-      <c r="J59" s="11">
-        <v>0</v>
-      </c>
-      <c r="K59" s="11">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11">
-        <v>0</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O59" s="10" t="s">
+      <c r="Z59" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA59" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10">
-        <v>1</v>
-      </c>
-      <c r="S59" s="10">
-        <v>1</v>
-      </c>
-      <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="10">
-        <v>0</v>
-      </c>
-      <c r="V59" s="10">
-        <v>0</v>
-      </c>
-      <c r="W59" s="10">
-        <v>0</v>
-      </c>
-      <c r="X59" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y59" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z59" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="AA59" s="10" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>455</v>
-      </c>
       <c r="C60" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -8732,16 +8764,16 @@
         <v>0</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="O60" s="10" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q60" s="10">
         <v>1</v>
@@ -8768,30 +8800,30 @@
         <v>1</v>
       </c>
       <c r="Y60" s="10" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="Z60" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA60" s="10" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>463</v>
-      </c>
       <c r="E61" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -8815,99 +8847,99 @@
         <v>0</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q61" s="10">
+        <v>1</v>
+      </c>
+      <c r="R61" s="10">
+        <v>1</v>
+      </c>
+      <c r="S61" s="10">
+        <v>0</v>
+      </c>
+      <c r="T61" s="10">
+        <v>0</v>
+      </c>
+      <c r="U61" s="10">
+        <v>0</v>
+      </c>
+      <c r="V61" s="10">
+        <v>0</v>
+      </c>
+      <c r="W61" s="10">
+        <v>0</v>
+      </c>
+      <c r="X61" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="Z61" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="AA61" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q61" s="10">
-        <v>1</v>
-      </c>
-      <c r="R61" s="10">
-        <v>1</v>
-      </c>
-      <c r="S61" s="10">
-        <v>0</v>
-      </c>
-      <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="10">
-        <v>0</v>
-      </c>
-      <c r="V61" s="10">
-        <v>0</v>
-      </c>
-      <c r="W61" s="10">
-        <v>0</v>
-      </c>
-      <c r="X61" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y61" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="Z61" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="AA61" s="10" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>469</v>
       </c>
       <c r="C62" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="11">
+        <v>1</v>
+      </c>
+      <c r="H62" s="11">
+        <v>1</v>
+      </c>
+      <c r="I62" s="11">
+        <v>1</v>
+      </c>
+      <c r="J62" s="11">
+        <v>0</v>
+      </c>
+      <c r="K62" s="11">
+        <v>0</v>
+      </c>
+      <c r="L62" s="11">
+        <v>0</v>
+      </c>
+      <c r="M62" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="N62" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62" s="11">
-        <v>1</v>
-      </c>
-      <c r="H62" s="11">
-        <v>1</v>
-      </c>
-      <c r="I62" s="11">
-        <v>1</v>
-      </c>
-      <c r="J62" s="11">
-        <v>0</v>
-      </c>
-      <c r="K62" s="11">
-        <v>0</v>
-      </c>
-      <c r="L62" s="11">
-        <v>0</v>
-      </c>
-      <c r="M62" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="N62" s="10" t="s">
-        <v>426</v>
-      </c>
       <c r="O62" s="10" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q62" s="10">
         <v>1</v>
@@ -8916,10 +8948,10 @@
         <v>1</v>
       </c>
       <c r="S62" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U62" s="10">
         <v>0</v>
@@ -8934,13 +8966,13 @@
         <v>1</v>
       </c>
       <c r="Y62" s="10" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="Z62" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA62" s="10" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
@@ -8948,16 +8980,16 @@
         <v>480</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>479</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -8981,16 +9013,16 @@
         <v>0</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>474</v>
+        <v>267</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Q63" s="10">
         <v>1</v>
@@ -9002,7 +9034,7 @@
         <v>1</v>
       </c>
       <c r="T63" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U63" s="10">
         <v>0</v>
@@ -9017,30 +9049,30 @@
         <v>1</v>
       </c>
       <c r="Y63" s="10" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="Z63" s="10" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AA63" s="10" t="s">
-        <v>478</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B64" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>481</v>
-      </c>
       <c r="C64" s="10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -9064,16 +9096,16 @@
         <v>0</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="O64" s="10" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="P64" s="10" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="Q64" s="10">
         <v>1</v>
@@ -9085,7 +9117,7 @@
         <v>1</v>
       </c>
       <c r="T64" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U64" s="10">
         <v>0</v>
@@ -9100,30 +9132,30 @@
         <v>1</v>
       </c>
       <c r="Y64" s="10" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="Z64" s="10" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AA64" s="10" t="s">
-        <v>454</v>
+        <v>492</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -9147,16 +9179,16 @@
         <v>0</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>271</v>
+        <v>498</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="Q65" s="10">
         <v>1</v>
@@ -9171,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="U65" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" s="10">
         <v>0</v>
@@ -9183,30 +9215,30 @@
         <v>1</v>
       </c>
       <c r="Y65" s="10" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="Z65" s="10" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AA65" s="10" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -9230,16 +9262,16 @@
         <v>0</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>502</v>
+        <v>267</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>503</v>
+        <v>422</v>
       </c>
       <c r="O66" s="10" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="Q66" s="10">
         <v>1</v>
@@ -9254,7 +9286,7 @@
         <v>1</v>
       </c>
       <c r="U66" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" s="10">
         <v>0</v>
@@ -9266,30 +9298,30 @@
         <v>1</v>
       </c>
       <c r="Y66" s="10" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="Z66" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AA66" s="10" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -9313,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>271</v>
+        <v>514</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>426</v>
+        <v>515</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>493</v>
+        <v>487</v>
+      </c>
+      <c r="P67" s="10">
+        <v>1</v>
       </c>
       <c r="Q67" s="10">
         <v>1</v>
@@ -9349,30 +9381,30 @@
         <v>1</v>
       </c>
       <c r="Y67" s="10" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z67" s="10" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AA67" s="10" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -9396,28 +9428,26 @@
         <v>0</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>518</v>
+        <v>267</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>519</v>
+        <v>422</v>
       </c>
       <c r="O68" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="P68" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="10">
-        <v>1</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q68" s="10"/>
       <c r="R68" s="10">
         <v>1</v>
       </c>
       <c r="S68" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U68" s="10">
         <v>0</v>
@@ -9432,13 +9462,13 @@
         <v>1</v>
       </c>
       <c r="Y68" s="10" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z68" s="10" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA68" s="10" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
@@ -9446,16 +9476,16 @@
         <v>524</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>523</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -9479,20 +9509,22 @@
         <v>0</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>271</v>
+        <v>527</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q69" s="10"/>
+        <v>489</v>
+      </c>
+      <c r="Q69" s="10">
+        <v>1</v>
+      </c>
       <c r="R69" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" s="10">
         <v>0</v>
@@ -9513,165 +9545,76 @@
         <v>1</v>
       </c>
       <c r="Y69" s="10" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="Z69" s="10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AA69" s="10" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-      <c r="G70" s="11">
-        <v>1</v>
-      </c>
-      <c r="H70" s="11">
-        <v>1</v>
-      </c>
-      <c r="I70" s="11">
-        <v>1</v>
-      </c>
-      <c r="J70" s="11">
-        <v>0</v>
-      </c>
-      <c r="K70" s="11">
-        <v>0</v>
-      </c>
-      <c r="L70" s="11">
-        <v>0</v>
-      </c>
-      <c r="M70" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="N70" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O70" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="P70" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q70" s="10">
-        <v>1</v>
-      </c>
-      <c r="R70" s="10">
-        <v>0</v>
-      </c>
-      <c r="S70" s="10">
-        <v>0</v>
-      </c>
-      <c r="T70" s="10">
-        <v>0</v>
-      </c>
-      <c r="U70" s="10">
-        <v>0</v>
-      </c>
-      <c r="V70" s="10">
-        <v>0</v>
-      </c>
-      <c r="W70" s="10">
-        <v>0</v>
-      </c>
-      <c r="X70" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y70" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="Z70" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="AA70" s="10" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="Y1:AA1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A27" r:id="rId1" location="tab__1" xr:uid="{95368841-7C55-49E7-8EDD-4D0BC3A50641}"/>
-    <hyperlink ref="A28" r:id="rId2" xr:uid="{863A7B8C-92F4-4EB5-BFA2-C156E359FAF9}"/>
-    <hyperlink ref="A29" r:id="rId3" xr:uid="{46FDC48A-6B93-4697-B5A9-10F85829730C}"/>
-    <hyperlink ref="A30" r:id="rId4" xr:uid="{F3A68A9C-845E-4017-80EF-4DE7140FFCE5}"/>
-    <hyperlink ref="A31" r:id="rId5" xr:uid="{FE3150FF-D114-4199-AB58-D7C79CB01E11}"/>
-    <hyperlink ref="A32" r:id="rId6" xr:uid="{24E576CC-C690-4F36-929A-9BCF009A4BEA}"/>
-    <hyperlink ref="A33" r:id="rId7" xr:uid="{8B1877B0-C427-42C9-9CDE-6081B1CDDC92}"/>
-    <hyperlink ref="A34" r:id="rId8" xr:uid="{0201D03B-A464-4CD3-A19A-10B09D77D5FE}"/>
-    <hyperlink ref="A35" r:id="rId9" xr:uid="{C59D1F8C-5EF1-4930-B104-807C6E2E731D}"/>
-    <hyperlink ref="A36" r:id="rId10" xr:uid="{F94E2E37-2A9E-4A3C-949F-744E48AD3DE3}"/>
-    <hyperlink ref="A37" r:id="rId11" xr:uid="{C78C77A8-CD1A-4543-BA8B-E429B208DE13}"/>
-    <hyperlink ref="A38" r:id="rId12" xr:uid="{AC1A1959-B8B3-4DE0-8056-A352AF1D3028}"/>
-    <hyperlink ref="A39" r:id="rId13" xr:uid="{31BB7FE1-E4E8-4174-A6CA-E8E63CA74BE0}"/>
-    <hyperlink ref="A40" r:id="rId14" xr:uid="{ECFE2334-7903-4F70-9E8E-376326777A56}"/>
-    <hyperlink ref="A41" r:id="rId15" xr:uid="{99AF8707-5526-42F5-A69F-803F3B115EAE}"/>
-    <hyperlink ref="A42" r:id="rId16" xr:uid="{90944FE9-8007-4704-9D24-6CE238455130}"/>
-    <hyperlink ref="A43" r:id="rId17" xr:uid="{67743FE0-C7B4-46ED-BE6B-2A4CBB9BF024}"/>
-    <hyperlink ref="A44" r:id="rId18" xr:uid="{C251105B-20D8-40BB-A4E1-ED54C3CDB6EF}"/>
-    <hyperlink ref="A45" r:id="rId19" xr:uid="{9CC4E631-15C7-407A-B3D6-FF175C615A3A}"/>
-    <hyperlink ref="A46" r:id="rId20" xr:uid="{4EC21BBC-AF6E-4BA1-9665-F178F2204492}"/>
-    <hyperlink ref="A47" r:id="rId21" xr:uid="{80BD338A-CD91-4443-B1F1-AC3DFB9491CA}"/>
-    <hyperlink ref="A48" r:id="rId22" xr:uid="{C3066979-10E1-4575-A43D-67518170901D}"/>
-    <hyperlink ref="A49" r:id="rId23" xr:uid="{CBF096EB-5D9F-42DE-9158-91DC3862D99B}"/>
-    <hyperlink ref="A50" r:id="rId24" xr:uid="{03CA4655-6B5E-4902-A74C-40DFCCD6F968}"/>
-    <hyperlink ref="A51" r:id="rId25" xr:uid="{B75AEC44-7232-4851-89E4-11B7DC8F25A9}"/>
-    <hyperlink ref="A52" r:id="rId26" xr:uid="{5B4AD249-C4E2-432B-9053-D6C1B412D756}"/>
-    <hyperlink ref="A53" r:id="rId27" xr:uid="{178BE75C-31B5-4B2C-BA05-74BF385363F8}"/>
-    <hyperlink ref="A54" r:id="rId28" xr:uid="{39B84C5D-1F84-4E8B-B480-07C48F84D125}"/>
-    <hyperlink ref="A55" r:id="rId29" xr:uid="{D578DC11-DC00-4E2B-890B-ACC168FF02D5}"/>
-    <hyperlink ref="A57" r:id="rId30" xr:uid="{EBD7037D-745C-4673-B56E-F6B7D51B3686}"/>
-    <hyperlink ref="A58" r:id="rId31" xr:uid="{E435D359-2B74-4356-BB38-D195C7C48DA9}"/>
-    <hyperlink ref="A59" r:id="rId32" xr:uid="{8F628C28-8B1E-4342-827F-F48D1293E967}"/>
-    <hyperlink ref="A60" r:id="rId33" xr:uid="{9AF828C6-8790-4AD4-95F0-AC0D62FBC5F9}"/>
-    <hyperlink ref="A61" r:id="rId34" location="tab__1" xr:uid="{4CE74921-D718-4E65-BE87-5E9D8CE4702C}"/>
-    <hyperlink ref="A62" r:id="rId35" xr:uid="{D33222CB-7219-499D-8011-1785E659C8C0}"/>
-    <hyperlink ref="A63" r:id="rId36" location="tab__2" xr:uid="{5841EC36-D8FD-448F-BA3A-2BEC32F12FF6}"/>
-    <hyperlink ref="A64" r:id="rId37" xr:uid="{C737C6AD-A576-4245-9700-18B4AFF04361}"/>
-    <hyperlink ref="A65" r:id="rId38" xr:uid="{0FCF6939-79FD-4BA4-93C6-E7725DD7BD74}"/>
-    <hyperlink ref="A66" r:id="rId39" xr:uid="{AAD24000-6C89-4DDF-909E-506D3AFA45AA}"/>
-    <hyperlink ref="A67" r:id="rId40" xr:uid="{6503DE16-8DD8-446F-98AF-CB368024F23A}"/>
-    <hyperlink ref="A68" r:id="rId41" xr:uid="{E0AF42BE-36D0-4FC1-9AAC-18182CDEE8C7}"/>
-    <hyperlink ref="A69" r:id="rId42" xr:uid="{0474A9F5-A28A-46FA-85FD-2B4CFF6D4B08}"/>
-    <hyperlink ref="A70" r:id="rId43" xr:uid="{3111BF25-2977-4018-AC87-9C9BEA44E400}"/>
-    <hyperlink ref="N27" r:id="rId44" xr:uid="{10CF8333-2EC0-4143-BFA0-39E633209FC9}"/>
-    <hyperlink ref="N28" r:id="rId45" xr:uid="{180753F9-4B79-47E4-A598-4E25FB933709}"/>
-    <hyperlink ref="N29" r:id="rId46" xr:uid="{1379D46E-3DBC-4539-B5D1-6EFFB2E199E6}"/>
-    <hyperlink ref="N31" r:id="rId47" xr:uid="{8DCB9CEB-389A-4222-B554-F7CEE8BDB0C1}"/>
-    <hyperlink ref="N32" r:id="rId48" xr:uid="{2DB80A10-FA73-4681-A326-58CEC1A3E20B}"/>
-    <hyperlink ref="N33" r:id="rId49" xr:uid="{4C25E70E-74BE-4AEB-95C9-322562A77770}"/>
-    <hyperlink ref="N35" r:id="rId50" xr:uid="{BDB94C8C-F50D-4FFA-BEAF-B73B8EEB1CDA}"/>
-    <hyperlink ref="N36" r:id="rId51" xr:uid="{AD012CA2-5877-43A7-B421-1395E7532D3D}"/>
-    <hyperlink ref="N39" r:id="rId52" xr:uid="{D4A803DE-7180-4C41-B360-6DD399C0A547}"/>
-    <hyperlink ref="N40" r:id="rId53" xr:uid="{44CA4460-A0E2-43EB-B238-2D43FC910E10}"/>
-    <hyperlink ref="N43" r:id="rId54" xr:uid="{F614E41B-B227-4834-94B4-C3BE0ADAFC66}"/>
-    <hyperlink ref="N44" r:id="rId55" xr:uid="{3300E749-A1D1-40A8-AF13-28792ADCF04A}"/>
-    <hyperlink ref="N47" r:id="rId56" xr:uid="{FD461A68-C067-4799-97FA-EDE65BAB1B2A}"/>
-    <hyperlink ref="N48" r:id="rId57" xr:uid="{AE34E76D-7F4A-46A4-80FC-B81F825DC121}"/>
-    <hyperlink ref="N50" r:id="rId58" xr:uid="{8F28A0C9-A3BF-4538-A3FC-A3F607BD4B5A}"/>
-    <hyperlink ref="N51" r:id="rId59" xr:uid="{D46831DE-5F3C-41F9-A057-3025CAD317FC}"/>
+    <hyperlink ref="A26" r:id="rId1" location="tab__1" xr:uid="{95368841-7C55-49E7-8EDD-4D0BC3A50641}"/>
+    <hyperlink ref="A27" r:id="rId2" xr:uid="{863A7B8C-92F4-4EB5-BFA2-C156E359FAF9}"/>
+    <hyperlink ref="A28" r:id="rId3" xr:uid="{46FDC48A-6B93-4697-B5A9-10F85829730C}"/>
+    <hyperlink ref="A29" r:id="rId4" xr:uid="{F3A68A9C-845E-4017-80EF-4DE7140FFCE5}"/>
+    <hyperlink ref="A30" r:id="rId5" xr:uid="{FE3150FF-D114-4199-AB58-D7C79CB01E11}"/>
+    <hyperlink ref="A31" r:id="rId6" xr:uid="{24E576CC-C690-4F36-929A-9BCF009A4BEA}"/>
+    <hyperlink ref="A32" r:id="rId7" xr:uid="{8B1877B0-C427-42C9-9CDE-6081B1CDDC92}"/>
+    <hyperlink ref="A33" r:id="rId8" xr:uid="{0201D03B-A464-4CD3-A19A-10B09D77D5FE}"/>
+    <hyperlink ref="A34" r:id="rId9" xr:uid="{C59D1F8C-5EF1-4930-B104-807C6E2E731D}"/>
+    <hyperlink ref="A35" r:id="rId10" xr:uid="{F94E2E37-2A9E-4A3C-949F-744E48AD3DE3}"/>
+    <hyperlink ref="A36" r:id="rId11" xr:uid="{C78C77A8-CD1A-4543-BA8B-E429B208DE13}"/>
+    <hyperlink ref="A37" r:id="rId12" xr:uid="{AC1A1959-B8B3-4DE0-8056-A352AF1D3028}"/>
+    <hyperlink ref="A38" r:id="rId13" xr:uid="{31BB7FE1-E4E8-4174-A6CA-E8E63CA74BE0}"/>
+    <hyperlink ref="A39" r:id="rId14" xr:uid="{ECFE2334-7903-4F70-9E8E-376326777A56}"/>
+    <hyperlink ref="A40" r:id="rId15" xr:uid="{99AF8707-5526-42F5-A69F-803F3B115EAE}"/>
+    <hyperlink ref="A41" r:id="rId16" xr:uid="{90944FE9-8007-4704-9D24-6CE238455130}"/>
+    <hyperlink ref="A42" r:id="rId17" xr:uid="{67743FE0-C7B4-46ED-BE6B-2A4CBB9BF024}"/>
+    <hyperlink ref="A43" r:id="rId18" xr:uid="{C251105B-20D8-40BB-A4E1-ED54C3CDB6EF}"/>
+    <hyperlink ref="A44" r:id="rId19" xr:uid="{9CC4E631-15C7-407A-B3D6-FF175C615A3A}"/>
+    <hyperlink ref="A45" r:id="rId20" xr:uid="{4EC21BBC-AF6E-4BA1-9665-F178F2204492}"/>
+    <hyperlink ref="A46" r:id="rId21" xr:uid="{80BD338A-CD91-4443-B1F1-AC3DFB9491CA}"/>
+    <hyperlink ref="A47" r:id="rId22" xr:uid="{C3066979-10E1-4575-A43D-67518170901D}"/>
+    <hyperlink ref="A48" r:id="rId23" xr:uid="{CBF096EB-5D9F-42DE-9158-91DC3862D99B}"/>
+    <hyperlink ref="A49" r:id="rId24" xr:uid="{03CA4655-6B5E-4902-A74C-40DFCCD6F968}"/>
+    <hyperlink ref="A50" r:id="rId25" xr:uid="{B75AEC44-7232-4851-89E4-11B7DC8F25A9}"/>
+    <hyperlink ref="A51" r:id="rId26" xr:uid="{5B4AD249-C4E2-432B-9053-D6C1B412D756}"/>
+    <hyperlink ref="A52" r:id="rId27" xr:uid="{178BE75C-31B5-4B2C-BA05-74BF385363F8}"/>
+    <hyperlink ref="A53" r:id="rId28" xr:uid="{39B84C5D-1F84-4E8B-B480-07C48F84D125}"/>
+    <hyperlink ref="A54" r:id="rId29" xr:uid="{D578DC11-DC00-4E2B-890B-ACC168FF02D5}"/>
+    <hyperlink ref="A56" r:id="rId30" xr:uid="{EBD7037D-745C-4673-B56E-F6B7D51B3686}"/>
+    <hyperlink ref="A57" r:id="rId31" xr:uid="{E435D359-2B74-4356-BB38-D195C7C48DA9}"/>
+    <hyperlink ref="A58" r:id="rId32" xr:uid="{8F628C28-8B1E-4342-827F-F48D1293E967}"/>
+    <hyperlink ref="A59" r:id="rId33" xr:uid="{9AF828C6-8790-4AD4-95F0-AC0D62FBC5F9}"/>
+    <hyperlink ref="A60" r:id="rId34" location="tab__1" xr:uid="{4CE74921-D718-4E65-BE87-5E9D8CE4702C}"/>
+    <hyperlink ref="A61" r:id="rId35" xr:uid="{D33222CB-7219-499D-8011-1785E659C8C0}"/>
+    <hyperlink ref="A62" r:id="rId36" location="tab__2" xr:uid="{5841EC36-D8FD-448F-BA3A-2BEC32F12FF6}"/>
+    <hyperlink ref="A63" r:id="rId37" xr:uid="{C737C6AD-A576-4245-9700-18B4AFF04361}"/>
+    <hyperlink ref="A64" r:id="rId38" xr:uid="{0FCF6939-79FD-4BA4-93C6-E7725DD7BD74}"/>
+    <hyperlink ref="A65" r:id="rId39" xr:uid="{AAD24000-6C89-4DDF-909E-506D3AFA45AA}"/>
+    <hyperlink ref="A66" r:id="rId40" xr:uid="{6503DE16-8DD8-446F-98AF-CB368024F23A}"/>
+    <hyperlink ref="A67" r:id="rId41" xr:uid="{E0AF42BE-36D0-4FC1-9AAC-18182CDEE8C7}"/>
+    <hyperlink ref="A68" r:id="rId42" xr:uid="{0474A9F5-A28A-46FA-85FD-2B4CFF6D4B08}"/>
+    <hyperlink ref="A69" r:id="rId43" xr:uid="{3111BF25-2977-4018-AC87-9C9BEA44E400}"/>
+    <hyperlink ref="N26" r:id="rId44" xr:uid="{10CF8333-2EC0-4143-BFA0-39E633209FC9}"/>
+    <hyperlink ref="N27" r:id="rId45" xr:uid="{180753F9-4B79-47E4-A598-4E25FB933709}"/>
+    <hyperlink ref="N28" r:id="rId46" xr:uid="{1379D46E-3DBC-4539-B5D1-6EFFB2E199E6}"/>
+    <hyperlink ref="N30" r:id="rId47" xr:uid="{8DCB9CEB-389A-4222-B554-F7CEE8BDB0C1}"/>
+    <hyperlink ref="N31" r:id="rId48" xr:uid="{2DB80A10-FA73-4681-A326-58CEC1A3E20B}"/>
+    <hyperlink ref="N32" r:id="rId49" xr:uid="{4C25E70E-74BE-4AEB-95C9-322562A77770}"/>
+    <hyperlink ref="N34" r:id="rId50" xr:uid="{BDB94C8C-F50D-4FFA-BEAF-B73B8EEB1CDA}"/>
+    <hyperlink ref="N35" r:id="rId51" xr:uid="{AD012CA2-5877-43A7-B421-1395E7532D3D}"/>
+    <hyperlink ref="N38" r:id="rId52" xr:uid="{D4A803DE-7180-4C41-B360-6DD399C0A547}"/>
+    <hyperlink ref="N39" r:id="rId53" xr:uid="{44CA4460-A0E2-43EB-B238-2D43FC910E10}"/>
+    <hyperlink ref="N42" r:id="rId54" xr:uid="{F614E41B-B227-4834-94B4-C3BE0ADAFC66}"/>
+    <hyperlink ref="N43" r:id="rId55" xr:uid="{3300E749-A1D1-40A8-AF13-28792ADCF04A}"/>
+    <hyperlink ref="N46" r:id="rId56" xr:uid="{FD461A68-C067-4799-97FA-EDE65BAB1B2A}"/>
+    <hyperlink ref="N47" r:id="rId57" xr:uid="{AE34E76D-7F4A-46A4-80FC-B81F825DC121}"/>
+    <hyperlink ref="N49" r:id="rId58" xr:uid="{8F28A0C9-A3BF-4538-A3FC-A3F607BD4B5A}"/>
+    <hyperlink ref="N50" r:id="rId59" xr:uid="{D46831DE-5F3C-41F9-A057-3025CAD317FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId60"/>

--- a/Übungssammlung GGIE.xlsx
+++ b/Übungssammlung GGIE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carsteba\Nextcloud\Austausch_SOKO-L_Weiterentwicklung\Überarbeitung_Foliensätze\Block 7_SuS-Zusatzmodul\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6881D5F9-F8AE-4B92-9511-80DB741FF649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB2C750-903E-43E5-A8FA-0B7210CAEA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-73785" yWindow="-6720" windowWidth="57600" windowHeight="23445" activeTab="1" xr2:uid="{5F5F4A6B-6BC2-42AB-AA6B-D27BC4305A0A}"/>
+    <workbookView xWindow="-50355" yWindow="-6465" windowWidth="57600" windowHeight="23445" activeTab="1" xr2:uid="{5F5F4A6B-6BC2-42AB-AA6B-D27BC4305A0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -470,12 +470,6 @@
 Poster board (optional, for group mind-map version)</t>
   </si>
   <si>
-    <t>Students will:
-Reflect on experiences that bring them awe
-Experience the impact of feeling awe on systemic thinking
-Begin to recognize the benefits of seeking awe in their lives</t>
-  </si>
-  <si>
     <t>Appreciation of Beauty and Excellence
 Spirituality
 Transcendence</t>
@@ -485,12 +479,6 @@
   </si>
   <si>
     <t>—</t>
-  </si>
-  <si>
-    <t>Students will:
-Participate in a collaborative activity
-Experience how collaboration naturally promotes fair outcomes
-Develop skills for inclusive decision-making and resource-sharing</t>
   </si>
   <si>
     <t>Fairness
@@ -513,12 +501,6 @@
   <si>
     <t>Paper
 Pencil/pen</t>
-  </si>
-  <si>
-    <t>Students will:
-Create a systems map of a chosen topic
-Broaden their thinking about the topic
-Reflect on the vast interconnectedness of the system</t>
   </si>
   <si>
     <t>Awe
@@ -559,13 +541,6 @@
 String</t>
   </si>
   <si>
-    <t>Students will:
-Grow curious by considering multiple questions about a topic
-See connections among topics/ideas, and thus find greater meaning in what they might be learning about that day
-Reflect on what other classmates said
-Consider their own feelings about the ideas presented</t>
-  </si>
-  <si>
     <t>Awe
 Wonder
 Curiosity
@@ -581,11 +556,6 @@
     <t>Writing materials</t>
   </si>
   <si>
-    <t>Students will:
-Engage deeply with a topic or skill through questioning and exploration
-Reflect on the limitations of their own knowledge and existing knowledge</t>
-  </si>
-  <si>
     <t>Any time of the year
 To provide students with an opportunity to practice intellectual courage
 When discussing an idea or proposition with students
@@ -596,12 +566,6 @@
 Post-its
 Paper
 Pencil/pens</t>
-  </si>
-  <si>
-    <t>Students will:
-Evaluate various sides of a proposition or idea
-Share their personal opinions on a proposition or idea
-Identify gaps in their knowledge that if filled can better inform a decision</t>
   </si>
   <si>
     <t>Courage
@@ -635,11 +599,6 @@
 To encourage the practice of intellectual humility while learning</t>
   </si>
   <si>
-    <t>Students will:
-Reflect on and openly share how their understanding changes over time
-Listen to one another</t>
-  </si>
-  <si>
     <t>Humility
 Growth Mindset
 Open-Mindedness</t>
@@ -655,13 +614,6 @@
 Computers and internet or news articles that students can use to research the topic</t>
   </si>
   <si>
-    <t>Students will:
-Work with their peers to research and persuasively argue for and against a debate topic
-Respectfully listen to their classmates and paraphrase opposing arguments
-Entertain multiple perspectives
-Consider using the skills they learned through this activity (e.g., perspective-taking, empathy, self-control, critical thinking, communication, and civil discourse) in their personal lives</t>
-  </si>
-  <si>
     <t>Respect
 Perspective-Taking
 Empathy</t>
@@ -675,12 +627,6 @@
     <t>Paper
 Pencils/pens
 Signs that indicate “Yes”, “No”, and “Maybe” corners of the room</t>
-  </si>
-  <si>
-    <t>Students will:
-Decide where they stand on a controversial statement
-Discuss and summarize their position with others who share it
-Respectfully hear arguments from students with a differing position</t>
   </si>
   <si>
     <t>Respect
@@ -705,12 +651,6 @@
 Tokens (Optional)</t>
   </si>
   <si>
-    <t>Students will:
-Work together to decide on a set of classroom norms
-Think critically about how norms work
-Entertain multiple perspectives</t>
-  </si>
-  <si>
     <t>Perspective
 Social Intelligence
 Critical Thinking</t>
@@ -724,12 +664,6 @@
   <si>
     <t>Paper (one fresh sheet per student)
 Crayons or markers in a variety of colors</t>
-  </si>
-  <si>
-    <t>Students will:
-Normalize the experience of making mistakes
-Reinterpret the meaning of mistakes with a growth mindset—recognizing that mistakes are important for learning
-Understand that mistakes lead to greater synaptic activity in the brain</t>
   </si>
   <si>
     <t>Growth Mindset
@@ -747,11 +681,6 @@
     <t>Varies depending on activity</t>
   </si>
   <si>
-    <t>Students will:
-Brainstorm ways they can contribute to their communities leveraging their SEL skills
-Use SEL skills for social change</t>
-  </si>
-  <si>
     <t>Courage
 Justice
 Critical Thinking</t>
@@ -765,11 +694,6 @@
     <t>Chairs arranged in a circle (or all participants sitting on the floor in a circle) preferably with no furniture in the middle
 Talking piece
 Bell or chime (optional)</t>
-  </si>
-  <si>
-    <t>Students will:
-Practice self-assessment skills about their learning
-Increase collaboration in learning with other students</t>
   </si>
   <si>
     <t>Connection
@@ -810,39 +734,6 @@
 One or more controversial statements, potentially related to topic(s) being studied</t>
   </si>
   <si>
-    <t>Students will:
-Decide where they stand on a controversial statement
-Discuss and summarize their position with others who share it
-Hear arguments from other positions, and change their stance if desired
-Reflect on the process and their final thoughts</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>School staff will:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Self-assess instructional practices that promote SEL as an integral part of high quality teaching and learning
-Reflect and develop instructional practices that promote SEL
-Reflect on their own SEL competencies and the impact these have on their ability to implement practices that support SEL
-Receive self-reflective feedback that can be used as part of professional development or educator evaluations</t>
-    </r>
-  </si>
-  <si>
     <t>Open-Mindedness
 Critical Thinking
 Intellectual Humility</t>
@@ -859,13 +750,6 @@
 One flip chart marker per group, each a different color</t>
   </si>
   <si>
-    <t>Students will:
-Work in small groups (3-5 students) to brainstorm ideas in response to different prompts
-Read and reflect on ideas that other groups have recorded
-Communicate their group’s ideas by writing them on a shared poster
-Discuss all the responses as a class</t>
-  </si>
-  <si>
     <t>Critical Thinking
 Creativity
 Connection</t>
@@ -885,29 +769,6 @@
 Writing materials</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Staff members will:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Brainstorm a list of social-emotional competencies that they can model for students</t>
-    </r>
-  </si>
-  <si>
     <t>Reflection
 Integrity
 Leadership</t>
@@ -915,12 +776,6 @@
   <si>
     <t>To debrief an activity or game
 To deepen students’ understanding, awareness, and practice of SEL skills</t>
-  </si>
-  <si>
-    <t>Students will:
-Strengthen the skill of reflection
-Strengthen the skill of being present in the moment (mindfulness)
-Use reflective practice to make connections to prior learning</t>
   </si>
   <si>
     <t>Reflection
@@ -972,12 +827,6 @@
 To help staff explore solutions to a problem at school or to kick-off a brainstorming process</t>
   </si>
   <si>
-    <t>Students will:
-Examine and gain insight into their own thoughts, emotions, and ideas on a specific topic
-Reflect on the writing process
-Explore their personal “voice” without concern for self- or other-evaluation</t>
-  </si>
-  <si>
     <t>Creativity
 Critical Thinking
 Love of Learning</t>
@@ -991,23 +840,12 @@
     <t>A text conducive to contemplative engagement</t>
   </si>
   <si>
-    <t>Students will:
-Improve their understanding of a text
-Bring deeper insight, enjoyment, and relaxed awareness to the act of reading
-Engage with other readers and their responses to the text
-Counteract the urge to rush through a reading assignment</t>
-  </si>
-  <si>
     <t>Reflection</t>
   </si>
   <si>
     <t>Any time throughout the school year; however, using it at the beginning of the school year will help to build a trusting classroom climate and to cultivate positive relationships between the teacher and students right from the start.
 When giving corrective feedback in written or verbal form — for example, during a writing conference
 When offering counseling on academic or behavioral issues</t>
-  </si>
-  <si>
-    <t>Students will:
-Revise an assignment to meet the high expectations of which the teacher knows they are capable</t>
   </si>
   <si>
     <t>Care
@@ -1220,9 +1058,6 @@
     <t>SEL Kernel</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Cool Kid: An SEL Kernels Practice for First Grade</t>
   </si>
   <si>
@@ -1261,10 +1096,6 @@
   </si>
   <si>
     <t>https://ggie.berkeley.edu/wp-content/uploads/2020/01/Cool_Kid_Certificate_for_Greater_Good.pdf</t>
-  </si>
-  <si>
-    <t>Students will:
-Identify and acknowledge their peers’ strengths, attributes, and positive actions; Learn how to share and receive compliments; Participate in creating a supportive and cooperative classroom community</t>
   </si>
   <si>
     <t xml:space="preserve">Kindness, Self-Worth, Confidence </t>
@@ -1323,10 +1154,6 @@
   </si>
   <si>
     <t>https://ggie.berkeley.edu/wp-content/uploads/2020/02/Dear_Abby_Library_Pack.pdf</t>
-  </si>
-  <si>
-    <t>Students will:
-Imagine a difficult scenario and brainstorm how to respond; Discuss the potential outcomes of different solutions to the problem; Reflect on what makes certain solutions better than others</t>
   </si>
   <si>
     <t xml:space="preserve">Courage, Fairness, Integrity </t>
@@ -1394,10 +1221,6 @@
     <t>https://ggie.berkeley.edu/wp-content/uploads/2020/01/Feelings_Faces_Poster_Final.pdf</t>
   </si>
   <si>
-    <t>Students will:
-Identify their feelings and how they feel in their bodies; Build their feelings vocabulary; Discuss how they know what someone else is feeling</t>
-  </si>
-  <si>
     <t xml:space="preserve">Courage, Balance, Equanimity </t>
   </si>
   <si>
@@ -1457,12 +1280,6 @@
     <t>Journals (optional); Music</t>
   </si>
   <si>
-    <t>Students will:
-Practice taking time to reflect on themselves by drawing and/or writing
-Identify their positive experiences, attributes, and/or aspirations
-Develop positive identities and mindsets over time so that they can learn to draw on their strengths in pursuit of their goals</t>
-  </si>
-  <si>
     <t xml:space="preserve">Optimism, Self-Worth, Reflection </t>
   </si>
   <si>
@@ -1513,12 +1330,6 @@
     <t xml:space="preserve">Cooles Kind: Eine SE-Lernbaustein-Übung für die erste Klasse </t>
   </si>
   <si>
-    <t>Students will:
-Identify and acknowledge their peers’ strengths, attributes, and positive actions
-Learn how to share and receive compliments
-Participate in creating a supportive and cooperative classroom community</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Reflection Before the Practice
 Share a compliment with a colleague. Write your colleague a quick note or text today. You might also consider a short visit to share your compliment and/or appreciation out loud.
@@ -1557,12 +1368,6 @@
     <t>Integrated into your class schedule as part of a routine
 During a designated SEL block of 10-15 minutes per day for Kernels practice or as time allows
 When a dilemma arises in the classroom, in a book the class is reading, or as part of something being studied</t>
-  </si>
-  <si>
-    <t>Students will:
-Imagine a difficult scenario and brainstorm how to respond
-Discuss the potential outcomes of different solutions to the problem
-Reflect on what makes certain solutions better than others</t>
   </si>
   <si>
     <t>Instructions
@@ -1603,12 +1408,6 @@
   </si>
   <si>
     <t>https://ggie.berkeley.edu/practice/feelings-circle-an-sel-kernels-practice-for-first-grade/</t>
-  </si>
-  <si>
-    <t>Students will:
-Identify their feelings and how they feel in their bodies
-Build their feelings vocabulary
-Discuss how they know what someone else is feeling</t>
   </si>
   <si>
     <t>Instructions
@@ -2470,10 +2269,6 @@
   </si>
   <si>
     <t>Cards showing various singing styles (e.g., loud, quiet, quick, slow)</t>
-  </si>
-  <si>
-    <t>Students will:
-Practice self-control</t>
   </si>
   <si>
     <t xml:space="preserve">Self-Control </t>
@@ -2718,10 +2513,6 @@
     <t>As the teacher counts down from 10 to 1, the students must remember a series of motions that go with certain numbers.</t>
   </si>
   <si>
-    <t>Students will:
-Practice memory and attention</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oderliness; Self-Control </t>
   </si>
   <si>
@@ -2926,10 +2717,6 @@
 Shipwreck</t>
   </si>
   <si>
-    <t>Students will:
-Practice keeping track of, updating, and using information over short periods of time</t>
-  </si>
-  <si>
     <t>Reflection Before the Practice
 How well do you remember the multiple things you need to do? What strategies and practices help you to develop your working memory (e.g, making a written list, repeating the information out loud)?</t>
   </si>
@@ -3004,10 +2791,6 @@
   </si>
   <si>
     <t>A game of rounds in which students count to ten, say, “hocus pocus, everybody focus,” then, in subsequent rounds, begin replacing numbers with a hand motion.</t>
-  </si>
-  <si>
-    <t>Students will:
-Practice focusing and attention</t>
   </si>
   <si>
     <t xml:space="preserve">Noe </t>
@@ -3081,10 +2864,6 @@
   </si>
   <si>
     <t>A game from the Focus Power Games, Remember Power Games, or Stop and Think Power Games</t>
-  </si>
-  <si>
-    <t>Students will:
-Practice and build executive function skills</t>
   </si>
   <si>
     <t>Self-Control, Concentration, Orderliness</t>
@@ -3330,6 +3109,216 @@
 For emergent bilingual learners, incorporate color words from their home languages (e.g., say “azul” in addition to “blue” if you have Spanish-speaking children in your class).
 Give students who may need additional support extra time to prepare by practicing with them ahead of time (just the two of you) prior to playing the game with the whole class.
  </t>
+  </si>
+  <si>
+    <t>GGIE Prosocial Teaching Strategies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Grow curious by considering multiple questions about a topic
+See connections among topics/ideas, and thus find greater meaning in what they might be learning about that day
+Reflect on what other classmates said
+Consider their own feelings about the ideas presented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Examine and gain insight into their own thoughts, emotions, and ideas on a specific topic
+Reflect on the writing process
+Explore their personal “voice” without concern for self- or other-evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Improve their understanding of a text
+Bring deeper insight, enjoyment, and relaxed awareness to the act of reading
+Engage with other readers and their responses to the text
+Counteract the urge to rush through a reading assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Revise an assignment to meet the high expectations of which the teacher knows they are capable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Identify and acknowledge their peers’ strengths, attributes, and positive actions; Learn how to share and receive compliments; Participate in creating a supportive and cooperative classroom community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Imagine a difficult scenario and brainstorm how to respond; Discuss the potential outcomes of different solutions to the problem; Reflect on what makes certain solutions better than others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Identify their feelings and how they feel in their bodies; Build their feelings vocabulary; Discuss how they know what someone else is feeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Practice taking time to reflect on themselves by drawing and/or writing
+Identify their positive experiences, attributes, and/or aspirations
+Develop positive identities and mindsets over time so that they can learn to draw on their strengths in pursuit of their goals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Identify and acknowledge their peers’ strengths, attributes, and positive actions
+Learn how to share and receive compliments
+Participate in creating a supportive and cooperative classroom community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Imagine a difficult scenario and brainstorm how to respond
+Discuss the potential outcomes of different solutions to the problem
+Reflect on what makes certain solutions better than others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Identify their feelings and how they feel in their bodies
+Build their feelings vocabulary
+Discuss how they know what someone else is feeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Practice self-control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Practice memory and attention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Practice keeping track of, updating, and using information over short periods of time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Practice focusing and attention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Practice and build executive function skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Participate in a collaborative activity
+Experience how collaboration naturally promotes fair outcomes
+Develop skills for inclusive decision-making and resource-sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Create a systems map of a chosen topic
+Broaden their thinking about the topic
+Reflect on the vast interconnectedness of the system</t>
+  </si>
+  <si>
+    <t>Engage deeply with a topic or skill through questioning and exploration
+Reflect on the limitations of their own knowledge and existing knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Reflect on experiences that bring them awe
+Experience the impact of feeling awe on systemic thinking
+Begin to recognize the benefits of seeking awe in their lives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Evaluate various sides of a proposition or idea
+Share their personal opinions on a proposition or idea
+Identify gaps in their knowledge that if filled can better inform a decision</t>
+  </si>
+  <si>
+    <t>Reflect on and openly share how their understanding changes over time
+Listen to one another</t>
+  </si>
+  <si>
+    <t>Work with their peers to research and persuasively argue for and against a debate topic
+Respectfully listen to their classmates and paraphrase opposing arguments
+Entertain multiple perspectives
+Consider using the skills they learned through this activity (e.g., perspective-taking, empathy, self-control, critical thinking, communication, and civil discourse) in their personal lives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Decide where they stand on a controversial statement
+Discuss and summarize their position with others who share it
+Respectfully hear arguments from students with a differing position</t>
+  </si>
+  <si>
+    <t>Work together to decide on a set of classroom norms
+Think critically about how norms work
+Entertain multiple perspectives</t>
+  </si>
+  <si>
+    <t>Normalize the experience of making mistakes
+Reinterpret the meaning of mistakes with a growth mindset—recognizing that mistakes are important for learning
+Understand that mistakes lead to greater synaptic activity in the brain</t>
+  </si>
+  <si>
+    <t>Brainstorm ways they can contribute to their communities leveraging their SEL skills
+Use SEL skills for social change</t>
+  </si>
+  <si>
+    <t>Practice self-assessment skills about their learning
+Increase collaboration in learning with other students</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>School staff will:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Self-assess instructional practices that promote SEL as an integral part of high quality teaching and learning
+Reflect and develop instructional practices that promote SEL
+Reflect on their own SEL competencies and the impact these have on their ability to implement practices that support SEL
+Receive self-reflective feedback that can be used as part of professional development or educator evaluations</t>
+    </r>
+  </si>
+  <si>
+    <t>Decide where they stand on a controversial statement
+Discuss and summarize their position with others who share it
+Hear arguments from other positions, and change their stance if desired
+Reflect on the process and their final thoughts</t>
+  </si>
+  <si>
+    <t>Work in small groups (3-5 students) to brainstorm ideas in response to different prompts
+Read and reflect on ideas that other groups have recorded
+Communicate their group’s ideas by writing them on a shared poster
+Discuss all the responses as a class</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Staff members will:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Brainstorm a list of social-emotional competencies that they can model for students</t>
+    </r>
+  </si>
+  <si>
+    <t>Strengthen the skill of reflection
+Strengthen the skill of being present in the moment (mindfulness)
+Use reflective practice to make connections to prior learning</t>
   </si>
 </sst>
 </file>
@@ -3430,7 +3419,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3445,6 +3434,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -3969,22 +3961,22 @@
   <dimension ref="A1:AB69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="255.5703125" customWidth="1"/>
+    <col min="1" max="1" width="100.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="79.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="136" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="187.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="87.42578125" customWidth="1"/>
-    <col min="14" max="14" width="47.42578125" customWidth="1"/>
-    <col min="15" max="15" width="61.140625" customWidth="1"/>
-    <col min="16" max="16" width="36.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="113.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="252" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -3993,10 +3985,8 @@
     <col min="22" max="22" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="48.28515625" customWidth="1"/>
-    <col min="26" max="26" width="50.7109375" customWidth="1"/>
-    <col min="27" max="27" width="64.42578125" customWidth="1"/>
-    <col min="28" max="28" width="72.140625" customWidth="1"/>
+    <col min="25" max="27" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="62" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -4016,7 +4006,7 @@
         <v>77</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>72</v>
@@ -4034,7 +4024,7 @@
         <v>76</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>132</v>
@@ -4058,31 +4048,34 @@
         <v>138</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>139</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>495</v>
+      </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
@@ -4095,8 +4088,8 @@
       <c r="E2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>257</v>
+      <c r="F2" s="13">
+        <v>0</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -4117,16 +4110,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -4156,7 +4149,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>495</v>
+      </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
@@ -4169,8 +4165,8 @@
       <c r="E3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>257</v>
+      <c r="F3" s="13">
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -4191,16 +4187,16 @@
         <v>0</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -4230,7 +4226,10 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="375" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="330" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>495</v>
+      </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
@@ -4243,8 +4242,8 @@
       <c r="E4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>257</v>
+      <c r="F4" s="13">
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4265,16 +4264,16 @@
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>157</v>
+        <v>496</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Q4" s="1">
         <v>1</v>
@@ -4304,7 +4303,10 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>495</v>
+      </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
@@ -4317,8 +4319,8 @@
       <c r="E5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>257</v>
+      <c r="F5" s="13">
+        <v>0</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -4339,16 +4341,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>161</v>
+        <v>514</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4378,7 +4380,10 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>495</v>
+      </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
@@ -4391,8 +4396,8 @@
       <c r="E6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>257</v>
+      <c r="F6" s="13">
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4419,10 +4424,10 @@
         <v>141</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4452,7 +4457,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>495</v>
+      </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
@@ -4465,8 +4473,8 @@
       <c r="E7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>257</v>
+      <c r="F7" s="13">
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4487,16 +4495,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>164</v>
+        <v>516</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -4527,6 +4535,9 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>495</v>
+      </c>
       <c r="B8" t="s">
         <v>54</v>
       </c>
@@ -4539,8 +4550,8 @@
       <c r="E8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>257</v>
+      <c r="F8" s="13">
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4561,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -4600,7 +4611,10 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>495</v>
+      </c>
       <c r="B9" t="s">
         <v>55</v>
       </c>
@@ -4613,8 +4627,8 @@
       <c r="E9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>257</v>
+      <c r="F9" s="13">
+        <v>0</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -4635,16 +4649,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>171</v>
+        <v>517</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -4674,7 +4688,10 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
       <c r="B10" t="s">
         <v>56</v>
       </c>
@@ -4687,8 +4704,8 @@
       <c r="E10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>257</v>
+      <c r="F10" s="13">
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -4709,16 +4726,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>175</v>
+        <v>518</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -4748,7 +4765,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>495</v>
+      </c>
       <c r="B11" t="s">
         <v>57</v>
       </c>
@@ -4761,8 +4781,8 @@
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>257</v>
+      <c r="F11" s="13">
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -4783,16 +4803,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>179</v>
+        <v>519</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -4823,6 +4843,9 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="135" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>495</v>
+      </c>
       <c r="B12" t="s">
         <v>58</v>
       </c>
@@ -4835,8 +4858,8 @@
       <c r="E12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>257</v>
+      <c r="F12" s="13">
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -4857,16 +4880,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>183</v>
+        <v>520</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4896,7 +4919,10 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>495</v>
+      </c>
       <c r="B13" t="s">
         <v>59</v>
       </c>
@@ -4909,8 +4935,8 @@
       <c r="E13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>257</v>
+      <c r="F13" s="13">
+        <v>0</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -4931,16 +4957,16 @@
         <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>187</v>
+        <v>521</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>1</v>
@@ -4970,7 +4996,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>495</v>
+      </c>
       <c r="B14" t="s">
         <v>60</v>
       </c>
@@ -4983,8 +5012,8 @@
       <c r="E14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>257</v>
+      <c r="F14" s="13">
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -5005,16 +5034,16 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>191</v>
+        <v>522</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -5044,7 +5073,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>495</v>
+      </c>
       <c r="B15" t="s">
         <v>61</v>
       </c>
@@ -5057,8 +5089,8 @@
       <c r="E15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>257</v>
+      <c r="F15" s="13">
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -5079,16 +5111,16 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>195</v>
+        <v>523</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -5118,7 +5150,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="195" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>495</v>
+      </c>
       <c r="B16" t="s">
         <v>62</v>
       </c>
@@ -5131,8 +5166,8 @@
       <c r="E16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>257</v>
+      <c r="F16" s="13">
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -5153,16 +5188,16 @@
         <v>1</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>204</v>
+        <v>524</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="Q16">
         <v>1</v>
@@ -5192,7 +5227,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>495</v>
+      </c>
       <c r="B17" t="s">
         <v>63</v>
       </c>
@@ -5205,8 +5243,8 @@
       <c r="E17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>257</v>
+      <c r="F17" s="13">
+        <v>0</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -5227,16 +5265,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>203</v>
+        <v>525</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="Q17">
         <v>1</v>
@@ -5266,7 +5304,10 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>495</v>
+      </c>
       <c r="B18" t="s">
         <v>64</v>
       </c>
@@ -5279,8 +5320,8 @@
       <c r="E18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>257</v>
+      <c r="F18" s="13">
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -5301,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>208</v>
+        <v>526</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -5340,7 +5381,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>495</v>
+      </c>
       <c r="B19" t="s">
         <v>65</v>
       </c>
@@ -5353,8 +5397,8 @@
       <c r="E19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>257</v>
+      <c r="F19" s="13">
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -5375,16 +5419,16 @@
         <v>1</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>212</v>
+        <v>527</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -5414,7 +5458,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="300" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>495</v>
+      </c>
       <c r="B20" t="s">
         <v>66</v>
       </c>
@@ -5427,8 +5474,8 @@
       <c r="E20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>257</v>
+      <c r="F20" s="14">
+        <v>0</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -5449,16 +5496,16 @@
         <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>215</v>
+        <v>528</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -5485,19 +5532,22 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="AA20" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="AB20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>495</v>
+      </c>
       <c r="B21" t="s">
         <v>67</v>
       </c>
@@ -5510,8 +5560,8 @@
       <c r="E21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>257</v>
+      <c r="F21" s="14">
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -5532,16 +5582,16 @@
         <v>1</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -5568,19 +5618,22 @@
         <v>1</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="AB21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="315" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>495</v>
+      </c>
       <c r="B22" t="s">
         <v>68</v>
       </c>
@@ -5593,8 +5646,8 @@
       <c r="E22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>257</v>
+      <c r="F22" s="14">
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5615,16 +5668,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -5651,19 +5704,22 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="AA22" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="AB22" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>495</v>
+      </c>
       <c r="B23" t="s">
         <v>69</v>
       </c>
@@ -5676,8 +5732,8 @@
       <c r="E23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>257</v>
+      <c r="F23" s="14">
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5698,55 +5754,58 @@
         <v>1</v>
       </c>
       <c r="M23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z23" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O23" s="1" t="s">
+      <c r="AA23" t="s">
         <v>225</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>1</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>244</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>246</v>
       </c>
       <c r="AB23" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="390" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>495</v>
+      </c>
       <c r="B24" t="s">
         <v>70</v>
       </c>
@@ -5759,8 +5818,8 @@
       <c r="E24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>257</v>
+      <c r="F24" s="14">
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5781,16 +5840,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>229</v>
+        <v>498</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="Q24">
         <v>1</v>
@@ -5817,19 +5876,22 @@
         <v>0</v>
       </c>
       <c r="Y24" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="AA24" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="AB24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="225" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>495</v>
+      </c>
       <c r="B25" t="s">
         <v>71</v>
       </c>
@@ -5842,8 +5904,8 @@
       <c r="E25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>257</v>
+      <c r="F25" s="14">
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5864,16 +5926,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>232</v>
+        <v>499</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="Q25">
         <v>1</v>
@@ -5900,30 +5962,30 @@
         <v>1</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="AB25" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>275</v>
+      <c r="A26" s="12" t="s">
+        <v>252</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>80</v>
@@ -5950,16 +6012,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O26" s="10" t="s">
-        <v>270</v>
+        <v>247</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>500</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q26" s="10">
         <v>1</v>
@@ -5986,27 +6048,27 @@
         <v>1</v>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="AA26" s="10" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>276</v>
+      <c r="A27" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>80</v>
@@ -6033,16 +6095,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>282</v>
+        <v>258</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q27" s="10">
         <v>1</v>
@@ -6069,27 +6131,27 @@
         <v>1</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="AA27" s="10" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>287</v>
+      <c r="A28" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>80</v>
@@ -6116,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>292</v>
+        <v>267</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="Q28" s="10">
         <v>1</v>
@@ -6152,27 +6214,27 @@
         <v>1</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="AA28" s="10" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>297</v>
+      <c r="A29" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>80</v>
@@ -6199,16 +6261,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q29" s="10">
         <v>1</v>
@@ -6235,27 +6297,27 @@
         <v>1</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="AA29" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>307</v>
+      <c r="A30" s="12" t="s">
+        <v>281</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>80</v>
@@ -6282,16 +6344,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O30" s="10" t="s">
-        <v>309</v>
+        <v>247</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q30" s="10">
         <v>1</v>
@@ -6318,27 +6380,27 @@
         <v>1</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="AA30" s="10" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>312</v>
+      <c r="A31" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>80</v>
@@ -6365,16 +6427,16 @@
         <v>0</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>314</v>
+        <v>258</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q31" s="10">
         <v>1</v>
@@ -6401,24 +6463,24 @@
         <v>1</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="AA31" s="10" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>318</v>
+      <c r="A32" s="12" t="s">
+        <v>290</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10" t="s">
@@ -6446,60 +6508,60 @@
         <v>0</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="N32" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>1</v>
+      </c>
+      <c r="R32" s="10">
+        <v>1</v>
+      </c>
+      <c r="S32" s="10">
+        <v>1</v>
+      </c>
+      <c r="T32" s="10">
+        <v>0</v>
+      </c>
+      <c r="U32" s="10">
+        <v>0</v>
+      </c>
+      <c r="V32" s="10">
+        <v>1</v>
+      </c>
+      <c r="W32" s="10">
+        <v>1</v>
+      </c>
+      <c r="X32" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z32" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="O32" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="P32" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q32" s="10">
-        <v>1</v>
-      </c>
-      <c r="R32" s="10">
-        <v>1</v>
-      </c>
-      <c r="S32" s="10">
-        <v>1</v>
-      </c>
-      <c r="T32" s="10">
-        <v>0</v>
-      </c>
-      <c r="U32" s="10">
-        <v>0</v>
-      </c>
-      <c r="V32" s="10">
-        <v>1</v>
-      </c>
-      <c r="W32" s="10">
-        <v>1</v>
-      </c>
-      <c r="X32" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="Z32" s="10" t="s">
-        <v>320</v>
-      </c>
       <c r="AA32" s="10" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>321</v>
+      <c r="A33" s="12" t="s">
+        <v>292</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
@@ -6527,16 +6589,16 @@
         <v>0</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q33" s="10">
         <v>1</v>
@@ -6563,27 +6625,27 @@
         <v>1</v>
       </c>
       <c r="Y33" s="10" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="Z33" s="10" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="AA33" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>324</v>
+      <c r="A34" s="12" t="s">
+        <v>295</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>80</v>
@@ -6610,16 +6672,16 @@
         <v>0</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>309</v>
+        <v>247</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q34" s="10">
         <v>1</v>
@@ -6646,27 +6708,27 @@
         <v>1</v>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="AA34" s="10" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>329</v>
+      <c r="A35" s="12" t="s">
+        <v>300</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>80</v>
@@ -6693,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>314</v>
+        <v>258</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q35" s="10">
         <v>1</v>
@@ -6729,27 +6791,27 @@
         <v>1</v>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z35" s="10" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="AA35" s="10" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>333</v>
+      <c r="A36" s="12" t="s">
+        <v>304</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>80</v>
@@ -6776,16 +6838,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="O36" s="10" t="s">
-        <v>319</v>
+        <v>326</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="Q36" s="10">
         <v>1</v>
@@ -6812,27 +6874,27 @@
         <v>1</v>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="AA36" s="10" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>338</v>
+      <c r="A37" s="12" t="s">
+        <v>309</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>80</v>
@@ -6859,16 +6921,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q37" s="10">
         <v>1</v>
@@ -6895,27 +6957,27 @@
         <v>1</v>
       </c>
       <c r="Y37" s="10" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="AA37" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>344</v>
+      <c r="A38" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>80</v>
@@ -6942,16 +7004,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O38" s="10" t="s">
-        <v>309</v>
+        <v>247</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q38" s="10">
         <v>1</v>
@@ -6978,27 +7040,27 @@
         <v>1</v>
       </c>
       <c r="Y38" s="10" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="Z38" s="10" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="AA38" s="10" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>348</v>
+      <c r="A39" s="12" t="s">
+        <v>319</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>80</v>
@@ -7025,16 +7087,16 @@
         <v>0</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>314</v>
+        <v>258</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q39" s="10">
         <v>1</v>
@@ -7061,27 +7123,27 @@
         <v>1</v>
       </c>
       <c r="Y39" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z39" s="10" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="AA39" s="10" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>352</v>
+      <c r="A40" s="12" t="s">
+        <v>323</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>80</v>
@@ -7108,16 +7170,16 @@
         <v>0</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="O40" s="10" t="s">
-        <v>319</v>
+        <v>326</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="P40" s="10" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="Q40" s="10">
         <v>1</v>
@@ -7144,27 +7206,27 @@
         <v>1</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="AA40" s="10" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>357</v>
+      <c r="A41" s="12" t="s">
+        <v>328</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>80</v>
@@ -7191,16 +7253,16 @@
         <v>0</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q41" s="10">
         <v>1</v>
@@ -7227,27 +7289,27 @@
         <v>1</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="Z41" s="10" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="AA41" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>361</v>
+      <c r="A42" s="12" t="s">
+        <v>332</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>80</v>
@@ -7274,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O42" s="10" t="s">
-        <v>309</v>
+        <v>247</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="P42" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q42" s="10">
         <v>1</v>
@@ -7310,27 +7372,27 @@
         <v>1</v>
       </c>
       <c r="Y42" s="10" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="Z42" s="10" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="AA42" s="10" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>365</v>
+      <c r="A43" s="12" t="s">
+        <v>336</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>80</v>
@@ -7357,16 +7419,16 @@
         <v>0</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>314</v>
+        <v>258</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q43" s="10">
         <v>1</v>
@@ -7393,27 +7455,27 @@
         <v>1</v>
       </c>
       <c r="Y43" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z43" s="10" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="AA43" s="10" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
-        <v>369</v>
+      <c r="A44" s="12" t="s">
+        <v>340</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>80</v>
@@ -7440,16 +7502,16 @@
         <v>0</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="O44" s="10" t="s">
-        <v>319</v>
+        <v>326</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="P44" s="10" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="Q44" s="10">
         <v>1</v>
@@ -7476,27 +7538,27 @@
         <v>1</v>
       </c>
       <c r="Y44" s="10" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="Z44" s="10" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="AA44" s="10" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>373</v>
+      <c r="A45" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>80</v>
@@ -7523,16 +7585,16 @@
         <v>0</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q45" s="10">
         <v>1</v>
@@ -7559,27 +7621,27 @@
         <v>1</v>
       </c>
       <c r="Y45" s="10" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="Z45" s="10" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="AA45" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>377</v>
+      <c r="A46" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>80</v>
@@ -7606,16 +7668,16 @@
         <v>0</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O46" s="10" t="s">
-        <v>309</v>
+        <v>247</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q46" s="10">
         <v>1</v>
@@ -7642,27 +7704,27 @@
         <v>1</v>
       </c>
       <c r="Y46" s="10" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="Z46" s="10" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="AA46" s="10" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
-        <v>381</v>
+      <c r="A47" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>80</v>
@@ -7689,16 +7751,16 @@
         <v>0</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>314</v>
+        <v>258</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q47" s="10">
         <v>1</v>
@@ -7725,27 +7787,27 @@
         <v>1</v>
       </c>
       <c r="Y47" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z47" s="10" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="AA47" s="10" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>385</v>
+      <c r="A48" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>80</v>
@@ -7772,16 +7834,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O48" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q48" s="10">
         <v>1</v>
@@ -7808,27 +7870,27 @@
         <v>1</v>
       </c>
       <c r="Y48" s="10" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="Z48" s="10" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="AA48" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>389</v>
+      <c r="A49" s="12" t="s">
+        <v>360</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -7855,16 +7917,16 @@
         <v>0</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>309</v>
+        <v>247</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="Q49" s="10">
         <v>1</v>
@@ -7891,27 +7953,27 @@
         <v>1</v>
       </c>
       <c r="Y49" s="10" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="Z49" s="10" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="AA49" s="10" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
-        <v>394</v>
+      <c r="A50" s="12" t="s">
+        <v>365</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>80</v>
@@ -7938,16 +8000,16 @@
         <v>0</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O50" s="10" t="s">
-        <v>314</v>
+        <v>258</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="Q50" s="10">
         <v>1</v>
@@ -7974,27 +8036,27 @@
         <v>1</v>
       </c>
       <c r="Y50" s="10" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="Z50" s="10" t="s">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="AA50" s="10" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>396</v>
+      <c r="A51" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>80</v>
@@ -8021,16 +8083,16 @@
         <v>0</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>319</v>
+        <v>326</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="Q51" s="10">
         <v>1</v>
@@ -8057,27 +8119,27 @@
         <v>1</v>
       </c>
       <c r="Y51" s="10" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="Z51" s="10" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="AA51" s="10" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>404</v>
+      <c r="A52" s="12" t="s">
+        <v>375</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>80</v>
@@ -8104,16 +8166,16 @@
         <v>0</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>302</v>
+        <v>276</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="P52" s="10" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="Q52" s="10">
         <v>1</v>
@@ -8140,27 +8202,27 @@
         <v>1</v>
       </c>
       <c r="Y52" s="10" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="Z52" s="10" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="AA52" s="10" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>408</v>
+      <c r="A53" s="12" t="s">
+        <v>379</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>80</v>
@@ -8187,16 +8249,16 @@
         <v>0</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>413</v>
+        <v>383</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="Q53" s="10">
         <v>1</v>
@@ -8223,27 +8285,27 @@
         <v>1</v>
       </c>
       <c r="Y53" s="10" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="Z53" s="10" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="AA53" s="10" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
-        <v>418</v>
+      <c r="A54" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>80</v>
@@ -8270,16 +8332,16 @@
         <v>0</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O54" s="10" t="s">
-        <v>413</v>
+        <v>392</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="Q54" s="10">
         <v>1</v>
@@ -8306,24 +8368,24 @@
         <v>1</v>
       </c>
       <c r="Y54" s="10" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="Z54" s="10" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="AA54" s="10" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10" t="s">
@@ -8351,16 +8413,16 @@
         <v>0</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>413</v>
+        <v>392</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="Q55" s="10">
         <v>1</v>
@@ -8387,27 +8449,27 @@
         <v>1</v>
       </c>
       <c r="Y55" s="10" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="Z55" s="10" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="AA55" s="10" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
-        <v>430</v>
+      <c r="A56" s="12" t="s">
+        <v>400</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>80</v>
@@ -8434,16 +8496,16 @@
         <v>0</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O56" s="10" t="s">
-        <v>413</v>
+        <v>392</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="Q56" s="10">
         <v>1</v>
@@ -8470,27 +8532,27 @@
         <v>1</v>
       </c>
       <c r="Y56" s="10" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="Z56" s="10" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="AA56" s="10" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>437</v>
+      <c r="A57" s="12" t="s">
+        <v>407</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>80</v>
@@ -8517,16 +8579,16 @@
         <v>0</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>413</v>
+        <v>409</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="Q57" s="10">
         <v>1</v>
@@ -8553,27 +8615,27 @@
         <v>1</v>
       </c>
       <c r="Y57" s="10" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="Z57" s="10" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="AA57" s="10" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>443</v>
+      <c r="A58" s="12" t="s">
+        <v>413</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>80</v>
@@ -8600,16 +8662,16 @@
         <v>0</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O58" s="10" t="s">
-        <v>446</v>
+        <v>392</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Q58" s="10"/>
       <c r="R58" s="10">
@@ -8634,27 +8696,27 @@
         <v>1</v>
       </c>
       <c r="Y58" s="10" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="Z58" s="10" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="AA58" s="10" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
-        <v>453</v>
+      <c r="A59" s="12" t="s">
+        <v>422</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>80</v>
@@ -8681,16 +8743,16 @@
         <v>0</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="O59" s="10" t="s">
-        <v>446</v>
+        <v>424</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Q59" s="10">
         <v>1</v>
@@ -8717,27 +8779,27 @@
         <v>1</v>
       </c>
       <c r="Y59" s="10" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="Z59" s="10" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="AA59" s="10" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
-        <v>463</v>
+      <c r="A60" s="12" t="s">
+        <v>432</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>80</v>
@@ -8764,16 +8826,16 @@
         <v>0</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O60" s="10" t="s">
-        <v>446</v>
+        <v>392</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Q60" s="10">
         <v>1</v>
@@ -8800,27 +8862,27 @@
         <v>1</v>
       </c>
       <c r="Y60" s="10" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="Z60" s="10" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="AA60" s="10" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
-        <v>464</v>
+      <c r="A61" s="12" t="s">
+        <v>433</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>80</v>
@@ -8847,16 +8909,16 @@
         <v>0</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>446</v>
+        <v>392</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Q61" s="10">
         <v>1</v>
@@ -8883,27 +8945,27 @@
         <v>1</v>
       </c>
       <c r="Y61" s="10" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="Z61" s="10" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="AA61" s="10" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
-        <v>476</v>
+      <c r="A62" s="12" t="s">
+        <v>444</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>80</v>
@@ -8930,16 +8992,16 @@
         <v>0</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="O62" s="10" t="s">
-        <v>472</v>
+        <v>440</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Q62" s="10">
         <v>1</v>
@@ -8966,27 +9028,27 @@
         <v>1</v>
       </c>
       <c r="Y62" s="10" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="Z62" s="10" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="AA62" s="10" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
-        <v>480</v>
+      <c r="A63" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>80</v>
@@ -9013,16 +9075,16 @@
         <v>0</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="O63" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Q63" s="10">
         <v>1</v>
@@ -9049,27 +9111,27 @@
         <v>1</v>
       </c>
       <c r="Y63" s="10" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="Z63" s="10" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="AA63" s="10" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
-        <v>483</v>
+      <c r="A64" s="12" t="s">
+        <v>451</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>80</v>
@@ -9096,16 +9158,16 @@
         <v>0</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="O64" s="10" t="s">
-        <v>487</v>
+        <v>455</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="P64" s="10" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="Q64" s="10">
         <v>1</v>
@@ -9132,27 +9194,27 @@
         <v>1</v>
       </c>
       <c r="Y64" s="10" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="Z64" s="10" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="AA64" s="10" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
-        <v>496</v>
+      <c r="A65" s="12" t="s">
+        <v>463</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>80</v>
@@ -9179,16 +9241,16 @@
         <v>0</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="O65" s="10" t="s">
-        <v>500</v>
+        <v>466</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="Q65" s="10">
         <v>1</v>
@@ -9215,27 +9277,27 @@
         <v>1</v>
       </c>
       <c r="Y65" s="10" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="Z65" s="10" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="AA65" s="10" t="s">
-        <v>504</v>
+        <v>470</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
-        <v>505</v>
+      <c r="A66" s="12" t="s">
+        <v>471</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>80</v>
@@ -9262,16 +9324,16 @@
         <v>0</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O66" s="10" t="s">
-        <v>487</v>
+        <v>392</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="P66" s="10" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="Q66" s="10">
         <v>1</v>
@@ -9298,27 +9360,27 @@
         <v>1</v>
       </c>
       <c r="Y66" s="10" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="Z66" s="10" t="s">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="AA66" s="10" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
-        <v>510</v>
+      <c r="A67" s="12" t="s">
+        <v>476</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>512</v>
+        <v>478</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>80</v>
@@ -9345,13 +9407,13 @@
         <v>0</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>487</v>
+        <v>481</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="P67" s="10">
         <v>1</v>
@@ -9381,27 +9443,27 @@
         <v>1</v>
       </c>
       <c r="Y67" s="10" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="Z67" s="10" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="AA67" s="10" t="s">
-        <v>517</v>
+        <v>483</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
-        <v>520</v>
+      <c r="A68" s="12" t="s">
+        <v>486</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>518</v>
+        <v>484</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>521</v>
+        <v>487</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>80</v>
@@ -9428,16 +9490,16 @@
         <v>0</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O68" s="10" t="s">
-        <v>487</v>
+        <v>392</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="Q68" s="10"/>
       <c r="R68" s="10">
@@ -9462,27 +9524,27 @@
         <v>1</v>
       </c>
       <c r="Y68" s="10" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="Z68" s="10" t="s">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="AA68" s="10" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
-        <v>524</v>
+      <c r="A69" s="12" t="s">
+        <v>490</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>80</v>
@@ -9509,16 +9571,16 @@
         <v>0</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="O69" s="10" t="s">
-        <v>487</v>
+        <v>392</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="Q69" s="10">
         <v>1</v>
@@ -9545,78 +9607,35 @@
         <v>1</v>
       </c>
       <c r="Y69" s="10" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="Z69" s="10" t="s">
-        <v>528</v>
+        <v>494</v>
       </c>
       <c r="AA69" s="10" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" location="tab__1" xr:uid="{95368841-7C55-49E7-8EDD-4D0BC3A50641}"/>
-    <hyperlink ref="A27" r:id="rId2" xr:uid="{863A7B8C-92F4-4EB5-BFA2-C156E359FAF9}"/>
-    <hyperlink ref="A28" r:id="rId3" xr:uid="{46FDC48A-6B93-4697-B5A9-10F85829730C}"/>
-    <hyperlink ref="A29" r:id="rId4" xr:uid="{F3A68A9C-845E-4017-80EF-4DE7140FFCE5}"/>
-    <hyperlink ref="A30" r:id="rId5" xr:uid="{FE3150FF-D114-4199-AB58-D7C79CB01E11}"/>
-    <hyperlink ref="A31" r:id="rId6" xr:uid="{24E576CC-C690-4F36-929A-9BCF009A4BEA}"/>
-    <hyperlink ref="A32" r:id="rId7" xr:uid="{8B1877B0-C427-42C9-9CDE-6081B1CDDC92}"/>
-    <hyperlink ref="A33" r:id="rId8" xr:uid="{0201D03B-A464-4CD3-A19A-10B09D77D5FE}"/>
-    <hyperlink ref="A34" r:id="rId9" xr:uid="{C59D1F8C-5EF1-4930-B104-807C6E2E731D}"/>
-    <hyperlink ref="A35" r:id="rId10" xr:uid="{F94E2E37-2A9E-4A3C-949F-744E48AD3DE3}"/>
-    <hyperlink ref="A36" r:id="rId11" xr:uid="{C78C77A8-CD1A-4543-BA8B-E429B208DE13}"/>
-    <hyperlink ref="A37" r:id="rId12" xr:uid="{AC1A1959-B8B3-4DE0-8056-A352AF1D3028}"/>
-    <hyperlink ref="A38" r:id="rId13" xr:uid="{31BB7FE1-E4E8-4174-A6CA-E8E63CA74BE0}"/>
-    <hyperlink ref="A39" r:id="rId14" xr:uid="{ECFE2334-7903-4F70-9E8E-376326777A56}"/>
-    <hyperlink ref="A40" r:id="rId15" xr:uid="{99AF8707-5526-42F5-A69F-803F3B115EAE}"/>
-    <hyperlink ref="A41" r:id="rId16" xr:uid="{90944FE9-8007-4704-9D24-6CE238455130}"/>
-    <hyperlink ref="A42" r:id="rId17" xr:uid="{67743FE0-C7B4-46ED-BE6B-2A4CBB9BF024}"/>
-    <hyperlink ref="A43" r:id="rId18" xr:uid="{C251105B-20D8-40BB-A4E1-ED54C3CDB6EF}"/>
-    <hyperlink ref="A44" r:id="rId19" xr:uid="{9CC4E631-15C7-407A-B3D6-FF175C615A3A}"/>
-    <hyperlink ref="A45" r:id="rId20" xr:uid="{4EC21BBC-AF6E-4BA1-9665-F178F2204492}"/>
-    <hyperlink ref="A46" r:id="rId21" xr:uid="{80BD338A-CD91-4443-B1F1-AC3DFB9491CA}"/>
-    <hyperlink ref="A47" r:id="rId22" xr:uid="{C3066979-10E1-4575-A43D-67518170901D}"/>
-    <hyperlink ref="A48" r:id="rId23" xr:uid="{CBF096EB-5D9F-42DE-9158-91DC3862D99B}"/>
-    <hyperlink ref="A49" r:id="rId24" xr:uid="{03CA4655-6B5E-4902-A74C-40DFCCD6F968}"/>
-    <hyperlink ref="A50" r:id="rId25" xr:uid="{B75AEC44-7232-4851-89E4-11B7DC8F25A9}"/>
-    <hyperlink ref="A51" r:id="rId26" xr:uid="{5B4AD249-C4E2-432B-9053-D6C1B412D756}"/>
-    <hyperlink ref="A52" r:id="rId27" xr:uid="{178BE75C-31B5-4B2C-BA05-74BF385363F8}"/>
-    <hyperlink ref="A53" r:id="rId28" xr:uid="{39B84C5D-1F84-4E8B-B480-07C48F84D125}"/>
-    <hyperlink ref="A54" r:id="rId29" xr:uid="{D578DC11-DC00-4E2B-890B-ACC168FF02D5}"/>
-    <hyperlink ref="A56" r:id="rId30" xr:uid="{EBD7037D-745C-4673-B56E-F6B7D51B3686}"/>
-    <hyperlink ref="A57" r:id="rId31" xr:uid="{E435D359-2B74-4356-BB38-D195C7C48DA9}"/>
-    <hyperlink ref="A58" r:id="rId32" xr:uid="{8F628C28-8B1E-4342-827F-F48D1293E967}"/>
-    <hyperlink ref="A59" r:id="rId33" xr:uid="{9AF828C6-8790-4AD4-95F0-AC0D62FBC5F9}"/>
-    <hyperlink ref="A60" r:id="rId34" location="tab__1" xr:uid="{4CE74921-D718-4E65-BE87-5E9D8CE4702C}"/>
-    <hyperlink ref="A61" r:id="rId35" xr:uid="{D33222CB-7219-499D-8011-1785E659C8C0}"/>
-    <hyperlink ref="A62" r:id="rId36" location="tab__2" xr:uid="{5841EC36-D8FD-448F-BA3A-2BEC32F12FF6}"/>
-    <hyperlink ref="A63" r:id="rId37" xr:uid="{C737C6AD-A576-4245-9700-18B4AFF04361}"/>
-    <hyperlink ref="A64" r:id="rId38" xr:uid="{0FCF6939-79FD-4BA4-93C6-E7725DD7BD74}"/>
-    <hyperlink ref="A65" r:id="rId39" xr:uid="{AAD24000-6C89-4DDF-909E-506D3AFA45AA}"/>
-    <hyperlink ref="A66" r:id="rId40" xr:uid="{6503DE16-8DD8-446F-98AF-CB368024F23A}"/>
-    <hyperlink ref="A67" r:id="rId41" xr:uid="{E0AF42BE-36D0-4FC1-9AAC-18182CDEE8C7}"/>
-    <hyperlink ref="A68" r:id="rId42" xr:uid="{0474A9F5-A28A-46FA-85FD-2B4CFF6D4B08}"/>
-    <hyperlink ref="A69" r:id="rId43" xr:uid="{3111BF25-2977-4018-AC87-9C9BEA44E400}"/>
-    <hyperlink ref="N26" r:id="rId44" xr:uid="{10CF8333-2EC0-4143-BFA0-39E633209FC9}"/>
-    <hyperlink ref="N27" r:id="rId45" xr:uid="{180753F9-4B79-47E4-A598-4E25FB933709}"/>
-    <hyperlink ref="N28" r:id="rId46" xr:uid="{1379D46E-3DBC-4539-B5D1-6EFFB2E199E6}"/>
-    <hyperlink ref="N30" r:id="rId47" xr:uid="{8DCB9CEB-389A-4222-B554-F7CEE8BDB0C1}"/>
-    <hyperlink ref="N31" r:id="rId48" xr:uid="{2DB80A10-FA73-4681-A326-58CEC1A3E20B}"/>
-    <hyperlink ref="N32" r:id="rId49" xr:uid="{4C25E70E-74BE-4AEB-95C9-322562A77770}"/>
-    <hyperlink ref="N34" r:id="rId50" xr:uid="{BDB94C8C-F50D-4FFA-BEAF-B73B8EEB1CDA}"/>
-    <hyperlink ref="N35" r:id="rId51" xr:uid="{AD012CA2-5877-43A7-B421-1395E7532D3D}"/>
-    <hyperlink ref="N38" r:id="rId52" xr:uid="{D4A803DE-7180-4C41-B360-6DD399C0A547}"/>
-    <hyperlink ref="N39" r:id="rId53" xr:uid="{44CA4460-A0E2-43EB-B238-2D43FC910E10}"/>
-    <hyperlink ref="N42" r:id="rId54" xr:uid="{F614E41B-B227-4834-94B4-C3BE0ADAFC66}"/>
-    <hyperlink ref="N43" r:id="rId55" xr:uid="{3300E749-A1D1-40A8-AF13-28792ADCF04A}"/>
-    <hyperlink ref="N46" r:id="rId56" xr:uid="{FD461A68-C067-4799-97FA-EDE65BAB1B2A}"/>
-    <hyperlink ref="N47" r:id="rId57" xr:uid="{AE34E76D-7F4A-46A4-80FC-B81F825DC121}"/>
-    <hyperlink ref="N49" r:id="rId58" xr:uid="{8F28A0C9-A3BF-4538-A3FC-A3F607BD4B5A}"/>
-    <hyperlink ref="N50" r:id="rId59" xr:uid="{D46831DE-5F3C-41F9-A057-3025CAD317FC}"/>
+    <hyperlink ref="N26" r:id="rId1" xr:uid="{10CF8333-2EC0-4143-BFA0-39E633209FC9}"/>
+    <hyperlink ref="N27" r:id="rId2" xr:uid="{180753F9-4B79-47E4-A598-4E25FB933709}"/>
+    <hyperlink ref="N28" r:id="rId3" xr:uid="{1379D46E-3DBC-4539-B5D1-6EFFB2E199E6}"/>
+    <hyperlink ref="N30" r:id="rId4" xr:uid="{8DCB9CEB-389A-4222-B554-F7CEE8BDB0C1}"/>
+    <hyperlink ref="N31" r:id="rId5" xr:uid="{2DB80A10-FA73-4681-A326-58CEC1A3E20B}"/>
+    <hyperlink ref="N32" r:id="rId6" xr:uid="{4C25E70E-74BE-4AEB-95C9-322562A77770}"/>
+    <hyperlink ref="N34" r:id="rId7" xr:uid="{BDB94C8C-F50D-4FFA-BEAF-B73B8EEB1CDA}"/>
+    <hyperlink ref="N35" r:id="rId8" xr:uid="{AD012CA2-5877-43A7-B421-1395E7532D3D}"/>
+    <hyperlink ref="N38" r:id="rId9" xr:uid="{D4A803DE-7180-4C41-B360-6DD399C0A547}"/>
+    <hyperlink ref="N39" r:id="rId10" xr:uid="{44CA4460-A0E2-43EB-B238-2D43FC910E10}"/>
+    <hyperlink ref="N42" r:id="rId11" xr:uid="{F614E41B-B227-4834-94B4-C3BE0ADAFC66}"/>
+    <hyperlink ref="N43" r:id="rId12" xr:uid="{3300E749-A1D1-40A8-AF13-28792ADCF04A}"/>
+    <hyperlink ref="N46" r:id="rId13" xr:uid="{FD461A68-C067-4799-97FA-EDE65BAB1B2A}"/>
+    <hyperlink ref="N47" r:id="rId14" xr:uid="{AE34E76D-7F4A-46A4-80FC-B81F825DC121}"/>
+    <hyperlink ref="N49" r:id="rId15" xr:uid="{8F28A0C9-A3BF-4538-A3FC-A3F607BD4B5A}"/>
+    <hyperlink ref="N50" r:id="rId16" xr:uid="{D46831DE-5F3C-41F9-A057-3025CAD317FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId60"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId17"/>
 </worksheet>
 </file>